--- a/Data/National Accounts/PSA-12CNS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-12CNS_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF59AC71-B6F5-41F9-8519-DA1215634424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACC19BD-C319-4923-B140-8B92A5BA99B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="CNS" sheetId="12" r:id="rId1"/>
@@ -697,10 +697,10 @@
     <t>Percent Share to the Institutional Sector At Constant 2018 Prices</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -750,10 +750,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1242,7 +1244,7 @@
     </row>
     <row r="3" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:152" x14ac:dyDescent="0.2">
@@ -1252,7 +1254,7 @@
     </row>
     <row r="6" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:152" x14ac:dyDescent="0.2">
@@ -2032,28 +2034,28 @@
         <v>355277.59300039051</v>
       </c>
       <c r="CT12" s="10">
-        <v>208286.15817075479</v>
+        <v>208005.45861065586</v>
       </c>
       <c r="CU12" s="10">
-        <v>703553.88809073321</v>
+        <v>700454.51374385273</v>
       </c>
       <c r="CV12" s="10">
-        <v>343009.89157967363</v>
+        <v>342904.44009823009</v>
       </c>
       <c r="CW12" s="10">
-        <v>371641.88731891487</v>
+        <v>373373.39047105284</v>
       </c>
       <c r="CX12" s="10">
-        <v>227147.03567532424</v>
+        <v>226561.74900899277</v>
       </c>
       <c r="CY12" s="10">
-        <v>649462.94385074486</v>
+        <v>646912.46280068625</v>
       </c>
       <c r="CZ12" s="10">
-        <v>254098.92799109971</v>
+        <v>254836.19234305047</v>
       </c>
       <c r="DA12" s="10">
-        <v>219051.61509967269</v>
+        <v>232641.0861430286</v>
       </c>
       <c r="DB12" s="9"/>
       <c r="DC12" s="9"/>
@@ -2396,28 +2398,28 @@
         <v>287405.8710176709</v>
       </c>
       <c r="CT13" s="10">
-        <v>347603.67789935565</v>
+        <v>347720.66739377944</v>
       </c>
       <c r="CU13" s="10">
-        <v>339649.39580373664</v>
+        <v>339201.50043616822</v>
       </c>
       <c r="CV13" s="10">
-        <v>354546.23294789804</v>
+        <v>353137.84739027597</v>
       </c>
       <c r="CW13" s="10">
-        <v>304419.92587018432</v>
+        <v>302921.1424648001</v>
       </c>
       <c r="CX13" s="10">
-        <v>356493.25796198816</v>
+        <v>356556.45918079012</v>
       </c>
       <c r="CY13" s="10">
-        <v>365545.04309983255</v>
+        <v>365089.10945058445</v>
       </c>
       <c r="CZ13" s="10">
-        <v>408212.54036967835</v>
+        <v>406175.03431820776</v>
       </c>
       <c r="DA13" s="10">
-        <v>356316.50079113519</v>
+        <v>354288.92856924684</v>
       </c>
       <c r="DB13" s="9"/>
       <c r="DC13" s="9"/>
@@ -2760,28 +2762,28 @@
         <v>290560.22787699121</v>
       </c>
       <c r="CT14" s="10">
-        <v>247248.79219075292</v>
+        <v>248526.96384294942</v>
       </c>
       <c r="CU14" s="10">
-        <v>251984.55163534189</v>
+        <v>250263.03862082926</v>
       </c>
       <c r="CV14" s="10">
-        <v>272126.27633196855</v>
+        <v>273753.21756520355</v>
       </c>
       <c r="CW14" s="10">
-        <v>330218.25333787821</v>
+        <v>330572.82256996649</v>
       </c>
       <c r="CX14" s="10">
-        <v>283456.04302651162</v>
+        <v>284927.11406783195</v>
       </c>
       <c r="CY14" s="10">
-        <v>297949.9249404982</v>
+        <v>295915.25588688639</v>
       </c>
       <c r="CZ14" s="10">
-        <v>309136.25715205923</v>
+        <v>311014.28096204542</v>
       </c>
       <c r="DA14" s="10">
-        <v>337541.58847980632</v>
+        <v>336038.85603496339</v>
       </c>
       <c r="DB14" s="9"/>
       <c r="DC14" s="9"/>
@@ -3277,28 +3279,28 @@
         <v>933243.69189505256</v>
       </c>
       <c r="CT16" s="3">
-        <v>803138.62826086336</v>
+        <v>804253.08984738472</v>
       </c>
       <c r="CU16" s="3">
-        <v>1295187.8355298117</v>
+        <v>1289919.0528008502</v>
       </c>
       <c r="CV16" s="3">
-        <v>969682.40085954033</v>
+        <v>969795.50505370961</v>
       </c>
       <c r="CW16" s="3">
-        <v>1006280.0665269773</v>
+        <v>1006867.3555058194</v>
       </c>
       <c r="CX16" s="3">
-        <v>867096.33666382404</v>
+        <v>868045.32225761493</v>
       </c>
       <c r="CY16" s="3">
-        <v>1312957.9118910758</v>
+        <v>1307916.8281381573</v>
       </c>
       <c r="CZ16" s="3">
-        <v>971447.72551283729</v>
+        <v>972025.50762330368</v>
       </c>
       <c r="DA16" s="3">
-        <v>912909.70437061426</v>
+        <v>922968.87074723886</v>
       </c>
       <c r="DB16" s="9"/>
       <c r="DC16" s="9"/>
@@ -3902,28 +3904,28 @@
         <v>506403.31752860779</v>
       </c>
       <c r="CT19" s="10">
-        <v>369897.87078638759</v>
+        <v>370274.58860127639</v>
       </c>
       <c r="CU19" s="10">
-        <v>658063.61833107879</v>
+        <v>656073.97194870899</v>
       </c>
       <c r="CV19" s="10">
-        <v>468146.24270909955</v>
+        <v>468185.67649931577</v>
       </c>
       <c r="CW19" s="10">
-        <v>550984.79364934284</v>
+        <v>551193.84188044327</v>
       </c>
       <c r="CX19" s="10">
-        <v>398468.74609154515</v>
+        <v>398789.5285963685</v>
       </c>
       <c r="CY19" s="10">
-        <v>683081.41989793326</v>
+        <v>681177.75930530997</v>
       </c>
       <c r="CZ19" s="10">
-        <v>468808.83387243573</v>
+        <v>469010.27767124563</v>
       </c>
       <c r="DA19" s="10">
-        <v>514192.78526026534</v>
+        <v>520090.39122897363</v>
       </c>
       <c r="DB19" s="9"/>
       <c r="DC19" s="9"/>
@@ -4122,7 +4124,7 @@
     </row>
     <row r="27" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:152" x14ac:dyDescent="0.2">
@@ -4132,7 +4134,7 @@
     </row>
     <row r="30" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:152" x14ac:dyDescent="0.2">
@@ -4912,28 +4914,28 @@
         <v>307323.40649036749</v>
       </c>
       <c r="CT36" s="10">
-        <v>165446.17506798048</v>
+        <v>165223.20937035806</v>
       </c>
       <c r="CU36" s="10">
-        <v>583159.49228790554</v>
+        <v>580590.49281091895</v>
       </c>
       <c r="CV36" s="10">
-        <v>269941.8558591592</v>
+        <v>269803.88863858982</v>
       </c>
       <c r="CW36" s="10">
-        <v>320355.16484052083</v>
+        <v>321927.82610119291</v>
       </c>
       <c r="CX36" s="10">
-        <v>179078.27124608678</v>
+        <v>178725.38816735617</v>
       </c>
       <c r="CY36" s="10">
-        <v>535197.97829888493</v>
+        <v>533222.3656410249</v>
       </c>
       <c r="CZ36" s="10">
-        <v>199227.20189487221</v>
+        <v>199924.63257646226</v>
       </c>
       <c r="DA36" s="10">
-        <v>185997.06246358962</v>
+        <v>197557.7417245399</v>
       </c>
       <c r="DB36" s="9"/>
       <c r="DC36" s="9"/>
@@ -5276,28 +5278,28 @@
         <v>238296.6135505756</v>
       </c>
       <c r="CT37" s="10">
-        <v>303023.3957097127</v>
+        <v>303125.38126428711</v>
       </c>
       <c r="CU37" s="10">
-        <v>288096.15455961711</v>
+        <v>287716.24240715714</v>
       </c>
       <c r="CV37" s="10">
-        <v>267864.35877988592</v>
+        <v>266756.17998039647</v>
       </c>
       <c r="CW37" s="10">
-        <v>251362.78977379182</v>
+        <v>250175.79732129184</v>
       </c>
       <c r="CX37" s="10">
-        <v>308953.430826917</v>
+        <v>309160.92337507993</v>
       </c>
       <c r="CY37" s="10">
-        <v>309678.93689845456</v>
+        <v>309340.67485465959</v>
       </c>
       <c r="CZ37" s="10">
-        <v>306487.93749263661</v>
+        <v>305093.86320495472</v>
       </c>
       <c r="DA37" s="10">
-        <v>293963.30232981447</v>
+        <v>292317.16796835547</v>
       </c>
       <c r="DB37" s="9"/>
       <c r="DC37" s="9"/>
@@ -5640,28 +5642,28 @@
         <v>271897.900744238</v>
       </c>
       <c r="CT38" s="10">
-        <v>191585.03530042552</v>
+        <v>192575.44887913836</v>
       </c>
       <c r="CU38" s="10">
-        <v>201863.97437463116</v>
+        <v>200484.87610534488</v>
       </c>
       <c r="CV38" s="10">
-        <v>214507.6645982617</v>
+        <v>215755.94212591267</v>
       </c>
       <c r="CW38" s="10">
-        <v>308530.37881327432</v>
+        <v>308920.01762253942</v>
       </c>
       <c r="CX38" s="10">
-        <v>218482.53207690018</v>
+        <v>219717.87940968794</v>
       </c>
       <c r="CY38" s="10">
-        <v>237874.53038315516</v>
+        <v>236284.32151327297</v>
       </c>
       <c r="CZ38" s="10">
-        <v>244020.68161311786</v>
+        <v>245608.55737637941</v>
       </c>
       <c r="DA38" s="10">
-        <v>311642.50337671471</v>
+        <v>310281.19522308063</v>
       </c>
       <c r="DB38" s="9"/>
       <c r="DC38" s="9"/>
@@ -6157,28 +6159,28 @@
         <v>817517.92078518099</v>
       </c>
       <c r="CT40" s="3">
-        <v>660054.60607811867</v>
+        <v>660924.03951378353</v>
       </c>
       <c r="CU40" s="3">
-        <v>1073119.6212221538</v>
+        <v>1068791.6113234209</v>
       </c>
       <c r="CV40" s="3">
-        <v>752313.87923730677</v>
+        <v>752316.01074489893</v>
       </c>
       <c r="CW40" s="3">
-        <v>880248.33342758694</v>
+        <v>881023.64104502415</v>
       </c>
       <c r="CX40" s="3">
-        <v>706514.23414990399</v>
+        <v>707604.19095212407</v>
       </c>
       <c r="CY40" s="3">
-        <v>1082751.4455804946</v>
+        <v>1078847.3620089574</v>
       </c>
       <c r="CZ40" s="3">
-        <v>749735.82100062678</v>
+        <v>750627.05315779638</v>
       </c>
       <c r="DA40" s="3">
-        <v>791602.86817011889</v>
+        <v>800156.10491597606</v>
       </c>
       <c r="DB40" s="9"/>
       <c r="DC40" s="9"/>
@@ -6782,28 +6784,28 @@
         <v>446748.07117780054</v>
       </c>
       <c r="CT43" s="10">
-        <v>302042.29846480757</v>
+        <v>302349.62153476378</v>
       </c>
       <c r="CU43" s="10">
-        <v>493268.29284938739</v>
+        <v>491779.58624922263</v>
       </c>
       <c r="CV43" s="10">
-        <v>384936.16519899847</v>
+        <v>384904.04828828544</v>
       </c>
       <c r="CW43" s="10">
-        <v>481217.36059493828</v>
+        <v>481498.38459614036</v>
       </c>
       <c r="CX43" s="10">
-        <v>323130.88091002707</v>
+        <v>323733.14454374416</v>
       </c>
       <c r="CY43" s="10">
-        <v>503649.31771024852</v>
+        <v>502234.02706130687</v>
       </c>
       <c r="CZ43" s="10">
-        <v>383512.05092910072</v>
+        <v>383612.60812406125</v>
       </c>
       <c r="DA43" s="10">
-        <v>447221.9481113092</v>
+        <v>452445.3364596371</v>
       </c>
       <c r="DB43" s="9"/>
       <c r="DC43" s="9"/>
@@ -7288,7 +7290,7 @@
     </row>
     <row r="51" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:144" x14ac:dyDescent="0.2">
@@ -7312,7 +7314,7 @@
     </row>
     <row r="54" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="CX54" s="5"/>
       <c r="CY54" s="5"/>
@@ -8088,28 +8090,28 @@
         <v>18.105115623372711</v>
       </c>
       <c r="CP60" s="21">
-        <v>14.576488270197487</v>
+        <v>14.422077770058735</v>
       </c>
       <c r="CQ60" s="21">
-        <v>23.505939309764216</v>
+        <v>22.961857120093072</v>
       </c>
       <c r="CR60" s="21">
-        <v>4.8682555069075875</v>
+        <v>4.8360158742583081</v>
       </c>
       <c r="CS60" s="21">
-        <v>4.6060586541145483</v>
+        <v>5.093424923829204</v>
       </c>
       <c r="CT60" s="21">
-        <v>9.0552716849802124</v>
+        <v>8.921059342519726</v>
       </c>
       <c r="CU60" s="21">
-        <v>-7.6882446612266477</v>
+        <v>-7.6439011945244033</v>
       </c>
       <c r="CV60" s="21">
-        <v>-25.920816212940565</v>
+        <v>-25.683029280679818</v>
       </c>
       <c r="CW60" s="21">
-        <v>-41.058416025183078</v>
+        <v>-37.692108736103144</v>
       </c>
       <c r="CX60" s="22"/>
       <c r="CY60" s="22"/>
@@ -8436,28 +8438,28 @@
         <v>6.8998510046454697</v>
       </c>
       <c r="CP61" s="21">
-        <v>9.1218456031945578</v>
+        <v>9.1585716517359685</v>
       </c>
       <c r="CQ61" s="21">
-        <v>16.247663232666596</v>
+        <v>16.094367538648484</v>
       </c>
       <c r="CR61" s="21">
-        <v>15.091545593514155</v>
+        <v>14.634360449363641</v>
       </c>
       <c r="CS61" s="21">
-        <v>5.9198703186781074</v>
+        <v>5.3983836141521522</v>
       </c>
       <c r="CT61" s="21">
-        <v>2.5573895294647571</v>
+        <v>2.5410602864754281</v>
       </c>
       <c r="CU61" s="21">
-        <v>7.6242288713092421</v>
+        <v>7.6319264452333329</v>
       </c>
       <c r="CV61" s="21">
-        <v>15.136617578917225</v>
+        <v>15.018833953902686</v>
       </c>
       <c r="CW61" s="21">
-        <v>17.047693173370476</v>
+        <v>16.957478004499379</v>
       </c>
       <c r="CX61" s="22"/>
       <c r="CY61" s="22"/>
@@ -8784,28 +8786,28 @@
         <v>12.355948878444096</v>
       </c>
       <c r="CP62" s="21">
-        <v>4.9109378696527699</v>
+        <v>5.4532830338179537</v>
       </c>
       <c r="CQ62" s="21">
-        <v>8.5734865056487592</v>
+        <v>7.8317320257115455</v>
       </c>
       <c r="CR62" s="21">
-        <v>9.5150918993950313</v>
+        <v>10.169841676132108</v>
       </c>
       <c r="CS62" s="21">
-        <v>13.64881413765832</v>
+        <v>13.770843651015667</v>
       </c>
       <c r="CT62" s="21">
-        <v>14.644055695861496</v>
+        <v>14.646358552822747</v>
       </c>
       <c r="CU62" s="21">
-        <v>18.241345751891515</v>
+        <v>18.241693826480017</v>
       </c>
       <c r="CV62" s="21">
-        <v>13.600296641307068</v>
+        <v>13.611187378269591</v>
       </c>
       <c r="CW62" s="21">
-        <v>2.2177257216713855</v>
+        <v>1.6535035828119362</v>
       </c>
       <c r="CX62" s="22"/>
       <c r="CY62" s="22"/>
@@ -9278,28 +9280,28 @@
         <v>12.672912300619316</v>
       </c>
       <c r="CP64" s="21">
-        <v>9.1207347995020456</v>
+        <v>9.2721543215469069</v>
       </c>
       <c r="CQ64" s="21">
-        <v>18.399214976228521</v>
+        <v>17.917570752991836</v>
       </c>
       <c r="CR64" s="21">
-        <v>9.7391028951725502</v>
+        <v>9.7519029138083653</v>
       </c>
       <c r="CS64" s="21">
-        <v>7.8260775043243598</v>
+        <v>7.8890073675468528</v>
       </c>
       <c r="CT64" s="21">
-        <v>7.9634705830868029</v>
+        <v>7.9318604075659067</v>
       </c>
       <c r="CU64" s="21">
-        <v>1.3720076635830338</v>
+        <v>1.395263935223511</v>
       </c>
       <c r="CV64" s="21">
-        <v>0.18205184003876695</v>
+        <v>0.22994564915730109</v>
       </c>
       <c r="CW64" s="21">
-        <v>-9.2787649544342656</v>
+        <v>-8.3326253751103536</v>
       </c>
       <c r="CX64" s="22"/>
       <c r="CY64" s="22"/>
@@ -9879,28 +9881,28 @@
         <v>12.884376005380901</v>
       </c>
       <c r="CP67" s="21">
-        <v>8.9906720663158097</v>
+        <v>9.1016722397874616</v>
       </c>
       <c r="CQ67" s="21">
-        <v>17.367800940680709</v>
+        <v>17.012940993947055</v>
       </c>
       <c r="CR67" s="21">
-        <v>9.6783170067493103</v>
+        <v>9.6875556406408947</v>
       </c>
       <c r="CS67" s="21">
-        <v>8.8035513547393975</v>
+        <v>8.8448323305672574</v>
       </c>
       <c r="CT67" s="21">
-        <v>7.723990204219632</v>
+        <v>7.7010253668252489</v>
       </c>
       <c r="CU67" s="21">
-        <v>3.801729934607593</v>
+        <v>3.8263653840795229</v>
       </c>
       <c r="CV67" s="21">
-        <v>0.14153508089734146</v>
+        <v>0.17612695418098667</v>
       </c>
       <c r="CW67" s="21">
-        <v>-6.6774997809635863</v>
+        <v>-5.6429241925776381</v>
       </c>
       <c r="CX67" s="22"/>
       <c r="CY67" s="22"/>
@@ -10381,7 +10383,7 @@
     </row>
     <row r="75" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="CX75" s="5"/>
       <c r="CY75" s="5"/>
@@ -10405,7 +10407,7 @@
     </row>
     <row r="78" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="CX78" s="5"/>
       <c r="CY78" s="5"/>
@@ -11181,28 +11183,28 @@
         <v>15.512354103290221</v>
       </c>
       <c r="CP84" s="21">
-        <v>12.554281952093334</v>
+        <v>12.402596704697771</v>
       </c>
       <c r="CQ84" s="21">
-        <v>21.384212826293592</v>
+        <v>20.849477503643257</v>
       </c>
       <c r="CR84" s="21">
-        <v>4.4612966014584856</v>
+        <v>4.4079064567426514</v>
       </c>
       <c r="CS84" s="21">
-        <v>4.2404054084184395</v>
+        <v>4.7521338441506487</v>
       </c>
       <c r="CT84" s="21">
-        <v>8.2395958519470014</v>
+        <v>8.1720836003930515</v>
       </c>
       <c r="CU84" s="21">
-        <v>-8.2244248140167571</v>
+        <v>-8.1586122674110868</v>
       </c>
       <c r="CV84" s="21">
-        <v>-26.196253907797839</v>
+        <v>-25.900018126029636</v>
       </c>
       <c r="CW84" s="21">
-        <v>-41.940357803757379</v>
+        <v>-38.632909084895083</v>
       </c>
       <c r="CX84" s="22"/>
       <c r="CY84" s="22"/>
@@ -11529,28 +11531,28 @@
         <v>4.6066913752143392</v>
       </c>
       <c r="CP85" s="21">
-        <v>7.0459539051271207</v>
+        <v>7.0819812915551239</v>
       </c>
       <c r="CQ85" s="21">
-        <v>13.271224463458935</v>
+        <v>13.121853796698502</v>
       </c>
       <c r="CR85" s="21">
-        <v>14.308250596412407</v>
+        <v>13.835347144476273</v>
       </c>
       <c r="CS85" s="21">
-        <v>5.4831564865872764</v>
+        <v>4.9850409511568898</v>
       </c>
       <c r="CT85" s="21">
-        <v>1.9569561958460326</v>
+        <v>1.9911041713562838</v>
       </c>
       <c r="CU85" s="21">
-        <v>7.4915204515064886</v>
+        <v>7.5158886639778046</v>
       </c>
       <c r="CV85" s="21">
-        <v>14.419080944056887</v>
+        <v>14.371806953966583</v>
       </c>
       <c r="CW85" s="21">
-        <v>16.947819760577929</v>
+        <v>16.844703243992456</v>
       </c>
       <c r="CX85" s="22"/>
       <c r="CY85" s="22"/>
@@ -11877,28 +11879,28 @@
         <v>9.9729529318361045</v>
       </c>
       <c r="CP86" s="21">
-        <v>3.1112010136739627</v>
+        <v>3.6442422997075852</v>
       </c>
       <c r="CQ86" s="21">
-        <v>6.0341953426439545</v>
+        <v>5.3097888420029875</v>
       </c>
       <c r="CR86" s="21">
-        <v>8.8146602748797989</v>
+        <v>9.4478819145563904</v>
       </c>
       <c r="CS86" s="21">
-        <v>13.472880065924016</v>
+        <v>13.616183419204276</v>
       </c>
       <c r="CT86" s="21">
-        <v>14.039456022385338</v>
+        <v>14.094439705854882</v>
       </c>
       <c r="CU86" s="21">
-        <v>17.839020617761875</v>
+        <v>17.856431918144921</v>
       </c>
       <c r="CV86" s="21">
-        <v>13.758490667514977</v>
+        <v>13.836288797573459</v>
       </c>
       <c r="CW86" s="21">
-        <v>1.0086930743775611</v>
+        <v>0.44062460277480398</v>
       </c>
       <c r="CX86" s="22"/>
       <c r="CY86" s="22"/>
@@ -12370,28 +12372,28 @@
         <v>10.312077186391932</v>
       </c>
       <c r="CP88" s="21">
-        <v>7.173557942095357</v>
+        <v>7.3147284965251913</v>
       </c>
       <c r="CQ88" s="21">
-        <v>15.995041699085704</v>
+        <v>15.527220890715967</v>
       </c>
       <c r="CR88" s="21">
-        <v>9.0500261385875405</v>
+        <v>9.0503351066460311</v>
       </c>
       <c r="CS88" s="21">
-        <v>7.6732767621970623</v>
+        <v>7.7681135355233977</v>
       </c>
       <c r="CT88" s="21">
-        <v>7.0387552247892131</v>
+        <v>7.062861788577294</v>
       </c>
       <c r="CU88" s="21">
-        <v>0.89755365272058896</v>
+        <v>0.94085232135057595</v>
       </c>
       <c r="CV88" s="21">
-        <v>-0.34268385946748481</v>
+        <v>-0.22450108238827227</v>
       </c>
       <c r="CW88" s="21">
-        <v>-10.07050645722812</v>
+        <v>-9.1788156823042044</v>
       </c>
       <c r="CX88" s="22"/>
       <c r="CY88" s="22"/>
@@ -12971,28 +12973,28 @@
         <v>8.5475453197703786</v>
       </c>
       <c r="CP91" s="21">
-        <v>7.0936472804378923</v>
+        <v>7.2026133048070307</v>
       </c>
       <c r="CQ91" s="21">
-        <v>15.928453539328729</v>
+        <v>15.578576086363014</v>
       </c>
       <c r="CR91" s="21">
-        <v>9.0204278949880461</v>
+        <v>9.0113318430574907</v>
       </c>
       <c r="CS91" s="21">
-        <v>7.715598933927879</v>
+        <v>7.7785032908423375</v>
       </c>
       <c r="CT91" s="21">
-        <v>6.9819964132197896</v>
+        <v>7.0724490741662009</v>
       </c>
       <c r="CU91" s="21">
-        <v>2.104539256090149</v>
+        <v>2.1258387099431673</v>
       </c>
       <c r="CV91" s="21">
-        <v>-0.36996115165264598</v>
+        <v>-0.33552262439623348</v>
       </c>
       <c r="CW91" s="21">
-        <v>-7.064460941641812</v>
+        <v>-6.0338827846476875</v>
       </c>
       <c r="CX91" s="22"/>
       <c r="CY91" s="22"/>
@@ -13478,7 +13480,7 @@
     </row>
     <row r="98" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="CZ98" s="7"/>
       <c r="DA98" s="7"/>
@@ -13490,7 +13492,7 @@
     </row>
     <row r="101" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="102" spans="1:152" x14ac:dyDescent="0.2">
@@ -14270,28 +14272,28 @@
         <v>115.60381848478765</v>
       </c>
       <c r="CT107" s="29">
-        <v>125.8936074437331</v>
+        <v>125.89360744373312</v>
       </c>
       <c r="CU107" s="29">
         <v>120.64519182059186</v>
       </c>
       <c r="CV107" s="29">
-        <v>127.0680645237311</v>
+        <v>127.09395769960921</v>
       </c>
       <c r="CW107" s="29">
-        <v>116.00933217478344</v>
+        <v>115.9804652467938</v>
       </c>
       <c r="CX107" s="29">
-        <v>126.84232101123092</v>
+        <v>126.76528574487875</v>
       </c>
       <c r="CY107" s="29">
-        <v>121.35003684338432</v>
+        <v>121.32132942754311</v>
       </c>
       <c r="CZ107" s="29">
-        <v>127.54228618097146</v>
+        <v>127.46613014061035</v>
       </c>
       <c r="DA107" s="29">
-        <v>117.77154552779766</v>
+        <v>117.75852675386741</v>
       </c>
       <c r="DB107" s="9"/>
       <c r="DC107" s="9"/>
@@ -14634,28 +14636,28 @@
         <v>120.60845797822152</v>
       </c>
       <c r="CT108" s="29">
-        <v>114.71182846632395</v>
+        <v>114.71182846632392</v>
       </c>
       <c r="CU108" s="29">
         <v>117.89445656535182</v>
       </c>
       <c r="CV108" s="29">
-        <v>132.36036125255538</v>
+        <v>132.38225536751486</v>
       </c>
       <c r="CW108" s="29">
-        <v>121.10779250347279</v>
+        <v>121.0833124979589</v>
       </c>
       <c r="CX108" s="29">
-        <v>115.38737634595296</v>
+        <v>115.3303772314747</v>
       </c>
       <c r="CY108" s="29">
-        <v>118.04000839091513</v>
+        <v>118.0216955374904</v>
       </c>
       <c r="CZ108" s="29">
-        <v>133.19040994214845</v>
+        <v>133.13117151928722</v>
       </c>
       <c r="DA108" s="29">
-        <v>121.21121853208842</v>
+        <v>121.20017822819085</v>
       </c>
       <c r="DB108" s="9"/>
       <c r="DC108" s="9"/>
@@ -15001,25 +15003,25 @@
         <v>129.05433443851226</v>
       </c>
       <c r="CU109" s="29">
-        <v>124.82888658859652</v>
+        <v>124.82888658859655</v>
       </c>
       <c r="CV109" s="29">
-        <v>126.86086384913902</v>
+        <v>126.88096321604175</v>
       </c>
       <c r="CW109" s="29">
-        <v>107.02941298941897</v>
+        <v>107.00919452033828</v>
       </c>
       <c r="CX109" s="29">
-        <v>129.73853805701154</v>
+        <v>129.67862007103858</v>
       </c>
       <c r="CY109" s="29">
-        <v>125.25507647270051</v>
+        <v>125.2369408142316</v>
       </c>
       <c r="CZ109" s="29">
-        <v>126.68444949357971</v>
+        <v>126.63006708086148</v>
       </c>
       <c r="DA109" s="29">
-        <v>108.31051118588427</v>
+        <v>108.30139280382878</v>
       </c>
       <c r="DB109" s="9"/>
       <c r="DC109" s="9"/>
@@ -15515,28 +15517,28 @@
         <v>114.15574731361527</v>
       </c>
       <c r="CT111" s="29">
-        <v>121.67760377174164</v>
+        <v>121.68616085428559</v>
       </c>
       <c r="CU111" s="29">
-        <v>120.69370552136107</v>
+        <v>120.68948138576989</v>
       </c>
       <c r="CV111" s="29">
-        <v>128.89332865194524</v>
+        <v>128.90799759711021</v>
       </c>
       <c r="CW111" s="29">
-        <v>114.3177474257335</v>
+        <v>114.28380676726518</v>
       </c>
       <c r="CX111" s="29">
-        <v>122.72878517545178</v>
+        <v>122.67385260813784</v>
       </c>
       <c r="CY111" s="29">
-        <v>121.26124765293302</v>
+        <v>121.23279661199172</v>
       </c>
       <c r="CZ111" s="29">
-        <v>129.57200367141391</v>
+        <v>129.49513390626024</v>
       </c>
       <c r="DA111" s="29">
-        <v>115.32420372363103</v>
+        <v>115.34860073887199</v>
       </c>
       <c r="DB111" s="9"/>
       <c r="DC111" s="9"/>
@@ -16140,28 +16142,28 @@
         <v>113.35321855862365</v>
       </c>
       <c r="CT114" s="29">
-        <v>122.46558600118924</v>
+        <v>122.46570269270296</v>
       </c>
       <c r="CU114" s="29">
-        <v>133.40886245287399</v>
+        <v>133.40813451663399</v>
       </c>
       <c r="CV114" s="29">
-        <v>121.6165912774354</v>
+        <v>121.63698422539169</v>
       </c>
       <c r="CW114" s="29">
-        <v>114.49811223937346</v>
+        <v>114.47470220336469</v>
       </c>
       <c r="CX114" s="29">
-        <v>123.31496914480769</v>
+        <v>123.18464615614371</v>
       </c>
       <c r="CY114" s="29">
-        <v>135.62639635916526</v>
+        <v>135.62955168351419</v>
       </c>
       <c r="CZ114" s="29">
-        <v>122.24096550204722</v>
+        <v>122.26143451457325</v>
       </c>
       <c r="DA114" s="29">
-        <v>114.97485475204981</v>
+        <v>114.9509895048661</v>
       </c>
       <c r="DB114" s="9"/>
       <c r="DC114" s="9"/>
@@ -16340,7 +16342,7 @@
     </row>
     <row r="122" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="124" spans="1:152" x14ac:dyDescent="0.2">
@@ -16350,7 +16352,7 @@
     </row>
     <row r="125" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="126" spans="1:152" x14ac:dyDescent="0.2">
@@ -17130,28 +17132,28 @@
         <v>38.069112717918387</v>
       </c>
       <c r="CT131" s="29">
-        <v>25.934023198682759</v>
+        <v>25.863184268291345</v>
       </c>
       <c r="CU131" s="29">
-        <v>54.320606539895145</v>
+        <v>54.302206965850239</v>
       </c>
       <c r="CV131" s="29">
-        <v>35.373426523532316</v>
+        <v>35.358427453140159</v>
       </c>
       <c r="CW131" s="29">
-        <v>36.932251734010826</v>
+        <v>37.082679106572229</v>
       </c>
       <c r="CX131" s="29">
-        <v>26.196285933957284</v>
+        <v>26.100221175059186</v>
       </c>
       <c r="CY131" s="29">
-        <v>49.465633130258702</v>
+        <v>49.461284455035084</v>
       </c>
       <c r="CZ131" s="29">
-        <v>26.15672684363518</v>
+        <v>26.217027263631138</v>
       </c>
       <c r="DA131" s="29">
-        <v>23.994882960598286</v>
+        <v>25.205734832062269</v>
       </c>
       <c r="DB131" s="9"/>
       <c r="DC131" s="9"/>
@@ -17494,28 +17496,28 @@
         <v>30.79644400639474</v>
       </c>
       <c r="CT132" s="29">
-        <v>43.280657369458794</v>
+        <v>43.235229280842802</v>
       </c>
       <c r="CU132" s="29">
-        <v>26.223948873392487</v>
+        <v>26.296340045497207</v>
       </c>
       <c r="CV132" s="29">
-        <v>36.563129601364651</v>
+        <v>36.413640355109536</v>
       </c>
       <c r="CW132" s="29">
-        <v>30.252007964427179</v>
+        <v>30.085506378605526</v>
       </c>
       <c r="CX132" s="29">
-        <v>41.113454513440267</v>
+        <v>41.075788330205732</v>
       </c>
       <c r="CY132" s="29">
-        <v>27.84133747085097</v>
+        <v>27.913786381225425</v>
       </c>
       <c r="CZ132" s="29">
-        <v>42.021050608171294</v>
+        <v>41.786458393601727</v>
       </c>
       <c r="DA132" s="29">
-        <v>39.030859140312224</v>
+        <v>38.385793908998608</v>
       </c>
       <c r="DB132" s="9"/>
       <c r="DC132" s="9"/>
@@ -17858,28 +17860,28 @@
         <v>31.134443275686884</v>
       </c>
       <c r="CT133" s="29">
-        <v>30.785319431858444</v>
+        <v>30.901586450865853</v>
       </c>
       <c r="CU133" s="29">
-        <v>19.455444586712371</v>
+        <v>19.401452988652554</v>
       </c>
       <c r="CV133" s="29">
-        <v>28.063443875103015</v>
+        <v>28.227932191750305</v>
       </c>
       <c r="CW133" s="29">
-        <v>32.815740301562002</v>
+        <v>32.831814514822241</v>
       </c>
       <c r="CX133" s="29">
-        <v>32.690259552602448</v>
+        <v>32.823990494735071</v>
       </c>
       <c r="CY133" s="29">
-        <v>22.693029398890314</v>
+        <v>22.624929163739484</v>
       </c>
       <c r="CZ133" s="29">
-        <v>31.822222548193523</v>
+        <v>31.996514342767135</v>
       </c>
       <c r="DA133" s="29">
-        <v>36.974257899089487</v>
+        <v>36.408471258939116</v>
       </c>
       <c r="DB133" s="9"/>
       <c r="DC133" s="9"/>
@@ -19296,7 +19298,7 @@
     </row>
     <row r="146" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="148" spans="1:152" x14ac:dyDescent="0.2">
@@ -19306,7 +19308,7 @@
     </row>
     <row r="149" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="150" spans="1:152" x14ac:dyDescent="0.2">
@@ -20086,28 +20088,28 @@
         <v>37.592253169838798</v>
       </c>
       <c r="CT155" s="29">
-        <v>25.065528449384022</v>
+        <v>24.998819757245695</v>
       </c>
       <c r="CU155" s="29">
-        <v>54.342449877466336</v>
+        <v>54.322141627965095</v>
       </c>
       <c r="CV155" s="29">
-        <v>35.881546693359603</v>
+        <v>35.86310603325402</v>
       </c>
       <c r="CW155" s="29">
-        <v>36.393725801569452</v>
+        <v>36.540202907533669</v>
       </c>
       <c r="CX155" s="29">
-        <v>25.346732251128433</v>
+        <v>25.257819336382166</v>
       </c>
       <c r="CY155" s="29">
-        <v>49.429440199172369</v>
+        <v>49.425190663496075</v>
       </c>
       <c r="CZ155" s="29">
-        <v>26.572986952787687</v>
+        <v>26.634349472937824</v>
       </c>
       <c r="DA155" s="29">
-        <v>23.496259291422632</v>
+        <v>24.689899947121607</v>
       </c>
       <c r="DB155" s="9"/>
       <c r="DC155" s="9"/>
@@ -20450,28 +20452,28 @@
         <v>29.148793866402929</v>
       </c>
       <c r="CT156" s="29">
-        <v>45.908837377895566</v>
+        <v>45.863875898247677</v>
       </c>
       <c r="CU156" s="29">
-        <v>26.846602080717748</v>
+        <v>26.9197698932999</v>
       </c>
       <c r="CV156" s="29">
-        <v>35.605399045867117</v>
+        <v>35.457995864832156</v>
       </c>
       <c r="CW156" s="29">
-        <v>28.555894993292824</v>
+        <v>28.396036799256191</v>
       </c>
       <c r="CX156" s="29">
-        <v>43.729257797425362</v>
+        <v>43.691222766655081</v>
       </c>
       <c r="CY156" s="29">
-        <v>28.60111045452603</v>
+        <v>28.673256824637921</v>
       </c>
       <c r="CZ156" s="29">
-        <v>40.879457657976886</v>
+        <v>40.645199493072106</v>
       </c>
       <c r="DA156" s="29">
-        <v>37.135199245720834</v>
+        <v>36.532517364102532</v>
       </c>
       <c r="DB156" s="9"/>
       <c r="DC156" s="9"/>
@@ -20814,28 +20816,28 @@
         <v>33.258952963758276</v>
       </c>
       <c r="CT157" s="29">
-        <v>29.025634172720409</v>
+        <v>29.137304344506632</v>
       </c>
       <c r="CU157" s="29">
-        <v>18.810948041815919</v>
+        <v>18.758088478735012</v>
       </c>
       <c r="CV157" s="29">
-        <v>28.513054260773284</v>
+        <v>28.67889810191383</v>
       </c>
       <c r="CW157" s="29">
-        <v>35.05037920513773</v>
+        <v>35.063760293210137</v>
       </c>
       <c r="CX157" s="29">
-        <v>30.924009951446195</v>
+        <v>31.05095789696275</v>
       </c>
       <c r="CY157" s="29">
-        <v>21.969449346301605</v>
+        <v>21.901552511866008</v>
       </c>
       <c r="CZ157" s="29">
-        <v>32.547555389235413</v>
+        <v>32.720451033990074</v>
       </c>
       <c r="DA157" s="29">
-        <v>39.36854146285652</v>
+        <v>38.777582688775844</v>
       </c>
       <c r="DB157" s="9"/>
       <c r="DC157" s="9"/>

--- a/Data/National Accounts/PSA-12CNS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-12CNS_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACC19BD-C319-4923-B140-8B92A5BA99B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918DEB39-D235-4C5E-BC56-C4F64EFCE102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="CNS" sheetId="12" r:id="rId1"/>
@@ -359,7 +359,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">CNS!$A$1:$DA$165</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">CNS!$A$1:$DB$165</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -533,7 +533,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="57">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -697,10 +697,13 @@
     <t>Percent Share to the Institutional Sector At Constant 2018 Prices</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>Q1 2000 to Q1 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>As of May 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1224,12 +1227,12 @@
   <sheetPr transitionEvaluation="1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:EV172"/>
+  <dimension ref="A1:EV174"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="49.140625" style="4" customWidth="1"/>
-    <col min="2" max="105" width="13" style="4" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="4"/>
+    <col min="2" max="106" width="13" style="4" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:152" x14ac:dyDescent="0.2">
@@ -1420,6 +1423,9 @@
       <c r="CY9" s="30"/>
       <c r="CZ9" s="30"/>
       <c r="DA9" s="30"/>
+      <c r="DB9" s="30">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
@@ -1736,6 +1742,9 @@
       </c>
       <c r="DA10" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2057,7 +2066,9 @@
       <c r="DA12" s="10">
         <v>232641.0861430286</v>
       </c>
-      <c r="DB12" s="9"/>
+      <c r="DB12" s="10">
+        <v>159081.32174658342</v>
+      </c>
       <c r="DC12" s="9"/>
       <c r="DD12" s="9"/>
       <c r="DE12" s="9"/>
@@ -2421,7 +2432,9 @@
       <c r="DA13" s="10">
         <v>354288.92856924684</v>
       </c>
-      <c r="DB13" s="9"/>
+      <c r="DB13" s="10">
+        <v>383204.48692269996</v>
+      </c>
       <c r="DC13" s="9"/>
       <c r="DD13" s="9"/>
       <c r="DE13" s="9"/>
@@ -2785,7 +2798,9 @@
       <c r="DA14" s="10">
         <v>336038.85603496339</v>
       </c>
-      <c r="DB14" s="9"/>
+      <c r="DB14" s="10">
+        <v>301400.43590238004</v>
+      </c>
       <c r="DC14" s="9"/>
       <c r="DD14" s="9"/>
       <c r="DE14" s="9"/>
@@ -3302,7 +3317,9 @@
       <c r="DA16" s="3">
         <v>922968.87074723886</v>
       </c>
-      <c r="DB16" s="9"/>
+      <c r="DB16" s="3">
+        <v>843686.24457166344</v>
+      </c>
       <c r="DC16" s="9"/>
       <c r="DD16" s="9"/>
       <c r="DE16" s="9"/>
@@ -3456,6 +3473,7 @@
       <c r="CY17" s="18"/>
       <c r="CZ17" s="18"/>
       <c r="DA17" s="18"/>
+      <c r="DB17" s="18"/>
     </row>
     <row r="18" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A18" s="11"/>
@@ -3563,7 +3581,7 @@
       <c r="CY18" s="3"/>
       <c r="CZ18" s="3"/>
       <c r="DA18" s="3"/>
-      <c r="DB18" s="9"/>
+      <c r="DB18" s="3"/>
       <c r="DC18" s="9"/>
       <c r="DD18" s="9"/>
       <c r="DE18" s="9"/>
@@ -3927,7 +3945,9 @@
       <c r="DA19" s="10">
         <v>520090.39122897363</v>
       </c>
-      <c r="DB19" s="9"/>
+      <c r="DB19" s="10">
+        <v>395509.7327156323</v>
+      </c>
       <c r="DC19" s="9"/>
       <c r="DD19" s="9"/>
       <c r="DE19" s="9"/>
@@ -4081,6 +4101,7 @@
       <c r="CY20" s="13"/>
       <c r="CZ20" s="13"/>
       <c r="DA20" s="13"/>
+      <c r="DB20" s="13"/>
     </row>
     <row r="21" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
@@ -4300,6 +4321,9 @@
       <c r="CY33" s="30"/>
       <c r="CZ33" s="30"/>
       <c r="DA33" s="30"/>
+      <c r="DB33" s="30">
+        <v>2026</v>
+      </c>
     </row>
     <row r="34" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
@@ -4616,6 +4640,9 @@
       </c>
       <c r="DA34" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB34" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -4937,7 +4964,9 @@
       <c r="DA36" s="10">
         <v>197557.7417245399</v>
       </c>
-      <c r="DB36" s="9"/>
+      <c r="DB36" s="10">
+        <v>122415.62714955705</v>
+      </c>
       <c r="DC36" s="9"/>
       <c r="DD36" s="9"/>
       <c r="DE36" s="9"/>
@@ -5301,7 +5330,9 @@
       <c r="DA37" s="10">
         <v>292317.16796835547</v>
       </c>
-      <c r="DB37" s="9"/>
+      <c r="DB37" s="10">
+        <v>325522.97854312538</v>
+      </c>
       <c r="DC37" s="9"/>
       <c r="DD37" s="9"/>
       <c r="DE37" s="9"/>
@@ -5665,7 +5696,9 @@
       <c r="DA38" s="10">
         <v>310281.19522308063</v>
       </c>
-      <c r="DB38" s="9"/>
+      <c r="DB38" s="10">
+        <v>227684.37666520762</v>
+      </c>
       <c r="DC38" s="9"/>
       <c r="DD38" s="9"/>
       <c r="DE38" s="9"/>
@@ -6182,7 +6215,9 @@
       <c r="DA40" s="3">
         <v>800156.10491597606</v>
       </c>
-      <c r="DB40" s="9"/>
+      <c r="DB40" s="3">
+        <v>675622.98235789011</v>
+      </c>
       <c r="DC40" s="9"/>
       <c r="DD40" s="9"/>
       <c r="DE40" s="9"/>
@@ -6336,6 +6371,7 @@
       <c r="CY41" s="18"/>
       <c r="CZ41" s="18"/>
       <c r="DA41" s="18"/>
+      <c r="DB41" s="18"/>
     </row>
     <row r="42" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A42" s="11"/>
@@ -6443,7 +6479,7 @@
       <c r="CY42" s="3"/>
       <c r="CZ42" s="3"/>
       <c r="DA42" s="3"/>
-      <c r="DB42" s="9"/>
+      <c r="DB42" s="3"/>
       <c r="DC42" s="9"/>
       <c r="DD42" s="9"/>
       <c r="DE42" s="9"/>
@@ -6807,7 +6843,9 @@
       <c r="DA43" s="10">
         <v>452445.3364596371</v>
       </c>
-      <c r="DB43" s="9"/>
+      <c r="DB43" s="10">
+        <v>314615.57233575423</v>
+      </c>
       <c r="DC43" s="9"/>
       <c r="DD43" s="9"/>
       <c r="DE43" s="9"/>
@@ -6961,6 +6999,7 @@
       <c r="CY44" s="13"/>
       <c r="CZ44" s="13"/>
       <c r="DA44" s="13"/>
+      <c r="DB44" s="13"/>
     </row>
     <row r="45" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A45" s="19" t="s">
@@ -7299,6 +7338,7 @@
       <c r="CY52" s="5"/>
       <c r="CZ52" s="5"/>
       <c r="DA52" s="5"/>
+      <c r="DB52" s="5"/>
     </row>
     <row r="53" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
@@ -7311,6 +7351,7 @@
       <c r="CY53" s="5"/>
       <c r="CZ53" s="5"/>
       <c r="DA53" s="5"/>
+      <c r="DB53" s="5"/>
     </row>
     <row r="54" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
@@ -7320,6 +7361,7 @@
       <c r="CY54" s="5"/>
       <c r="CZ54" s="5"/>
       <c r="DA54" s="5"/>
+      <c r="DB54" s="5"/>
     </row>
     <row r="55" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
@@ -7329,12 +7371,14 @@
       <c r="CY55" s="5"/>
       <c r="CZ55" s="5"/>
       <c r="DA55" s="5"/>
+      <c r="DB55" s="5"/>
     </row>
     <row r="56" spans="1:144" x14ac:dyDescent="0.2">
       <c r="CX56" s="5"/>
       <c r="CY56" s="5"/>
       <c r="CZ56" s="5"/>
       <c r="DA56" s="5"/>
+      <c r="DB56" s="5"/>
     </row>
     <row r="57" spans="1:144" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17"/>
@@ -7488,10 +7532,13 @@
       <c r="CU57" s="30"/>
       <c r="CV57" s="30"/>
       <c r="CW57" s="30"/>
-      <c r="CX57" s="31"/>
+      <c r="CX57" s="30" t="s">
+        <v>56</v>
+      </c>
       <c r="CY57" s="31"/>
       <c r="CZ57" s="31"/>
       <c r="DA57" s="31"/>
+      <c r="DB57" s="31"/>
     </row>
     <row r="58" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
@@ -7797,17 +7844,20 @@
       <c r="CW58" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="CX58" s="32"/>
+      <c r="CX58" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="CY58" s="32"/>
       <c r="CZ58" s="32"/>
       <c r="DA58" s="32"/>
+      <c r="DB58" s="32"/>
     </row>
     <row r="59" spans="1:144" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7"/>
-      <c r="CX59" s="5"/>
       <c r="CY59" s="5"/>
       <c r="CZ59" s="5"/>
       <c r="DA59" s="5"/>
+      <c r="DB59" s="5"/>
     </row>
     <row r="60" spans="1:144" s="25" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
@@ -8113,11 +8163,13 @@
       <c r="CW60" s="21">
         <v>-37.692108736103144</v>
       </c>
-      <c r="CX60" s="22"/>
+      <c r="CX60" s="21">
+        <v>-29.78456317431187</v>
+      </c>
       <c r="CY60" s="22"/>
       <c r="CZ60" s="22"/>
       <c r="DA60" s="22"/>
-      <c r="DB60" s="23"/>
+      <c r="DB60" s="22"/>
       <c r="DC60" s="23"/>
       <c r="DD60" s="23"/>
       <c r="DE60" s="23"/>
@@ -8461,11 +8513,13 @@
       <c r="CW61" s="21">
         <v>16.957478004499379</v>
       </c>
-      <c r="CX61" s="22"/>
+      <c r="CX61" s="21">
+        <v>7.4737189737454912</v>
+      </c>
       <c r="CY61" s="22"/>
       <c r="CZ61" s="22"/>
       <c r="DA61" s="22"/>
-      <c r="DB61" s="23"/>
+      <c r="DB61" s="22"/>
       <c r="DC61" s="23"/>
       <c r="DD61" s="23"/>
       <c r="DE61" s="23"/>
@@ -8809,11 +8863,13 @@
       <c r="CW62" s="21">
         <v>1.6535035828119362</v>
       </c>
-      <c r="CX62" s="22"/>
+      <c r="CX62" s="21">
+        <v>5.781591509267983</v>
+      </c>
       <c r="CY62" s="22"/>
       <c r="CZ62" s="22"/>
       <c r="DA62" s="22"/>
-      <c r="DB62" s="23"/>
+      <c r="DB62" s="22"/>
       <c r="DC62" s="23"/>
       <c r="DD62" s="23"/>
       <c r="DE62" s="23"/>
@@ -8955,11 +9011,11 @@
       <c r="CU63" s="23"/>
       <c r="CV63" s="23"/>
       <c r="CW63" s="23"/>
-      <c r="CX63" s="24"/>
+      <c r="CX63" s="23"/>
       <c r="CY63" s="24"/>
       <c r="CZ63" s="24"/>
       <c r="DA63" s="24"/>
-      <c r="DB63" s="23"/>
+      <c r="DB63" s="24"/>
       <c r="DC63" s="23"/>
       <c r="DD63" s="23"/>
       <c r="DE63" s="23"/>
@@ -9303,11 +9359,13 @@
       <c r="CW64" s="21">
         <v>-8.3326253751103536</v>
       </c>
-      <c r="CX64" s="22"/>
+      <c r="CX64" s="21">
+        <v>-2.8061988310239769</v>
+      </c>
       <c r="CY64" s="22"/>
       <c r="CZ64" s="22"/>
       <c r="DA64" s="22"/>
-      <c r="DB64" s="23"/>
+      <c r="DB64" s="22"/>
       <c r="DC64" s="23"/>
       <c r="DD64" s="23"/>
       <c r="DE64" s="23"/>
@@ -9449,10 +9507,11 @@
       <c r="CU65" s="26"/>
       <c r="CV65" s="26"/>
       <c r="CW65" s="26"/>
-      <c r="CX65" s="27"/>
+      <c r="CX65" s="26"/>
       <c r="CY65" s="27"/>
       <c r="CZ65" s="27"/>
       <c r="DA65" s="27"/>
+      <c r="DB65" s="27"/>
     </row>
     <row r="66" spans="1:144" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="11"/>
@@ -9556,11 +9615,11 @@
       <c r="CU66" s="21"/>
       <c r="CV66" s="21"/>
       <c r="CW66" s="21"/>
-      <c r="CX66" s="22"/>
+      <c r="CX66" s="21"/>
       <c r="CY66" s="22"/>
       <c r="CZ66" s="22"/>
       <c r="DA66" s="22"/>
-      <c r="DB66" s="23"/>
+      <c r="DB66" s="22"/>
       <c r="DC66" s="23"/>
       <c r="DD66" s="23"/>
       <c r="DE66" s="23"/>
@@ -9904,11 +9963,13 @@
       <c r="CW67" s="21">
         <v>-5.6429241925776381</v>
       </c>
-      <c r="CX67" s="22"/>
+      <c r="CX67" s="21">
+        <v>-0.82243781382128134</v>
+      </c>
       <c r="CY67" s="22"/>
       <c r="CZ67" s="22"/>
       <c r="DA67" s="22"/>
-      <c r="DB67" s="23"/>
+      <c r="DB67" s="22"/>
       <c r="DC67" s="23"/>
       <c r="DD67" s="23"/>
       <c r="DE67" s="23"/>
@@ -10050,28 +10111,29 @@
       <c r="CU68" s="13"/>
       <c r="CV68" s="13"/>
       <c r="CW68" s="13"/>
-      <c r="CX68" s="33"/>
+      <c r="CX68" s="13"/>
       <c r="CY68" s="33"/>
       <c r="CZ68" s="33"/>
       <c r="DA68" s="33"/>
+      <c r="DB68" s="33"/>
     </row>
     <row r="69" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A69" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="CX69" s="5"/>
       <c r="CY69" s="5"/>
       <c r="CZ69" s="5"/>
       <c r="DA69" s="5"/>
+      <c r="DB69" s="5"/>
     </row>
     <row r="70" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A70" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="CX70" s="5"/>
       <c r="CY70" s="5"/>
       <c r="CZ70" s="5"/>
       <c r="DA70" s="5"/>
+      <c r="DB70" s="5"/>
     </row>
     <row r="71" spans="1:144" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B71" s="9"/>
@@ -10174,11 +10236,11 @@
       <c r="CU71" s="9"/>
       <c r="CV71" s="9"/>
       <c r="CW71" s="9"/>
-      <c r="CX71" s="8"/>
+      <c r="CX71" s="9"/>
       <c r="CY71" s="8"/>
       <c r="CZ71" s="8"/>
       <c r="DA71" s="8"/>
-      <c r="DB71" s="9"/>
+      <c r="DB71" s="8"/>
       <c r="DC71" s="9"/>
       <c r="DD71" s="9"/>
       <c r="DE71" s="9"/>
@@ -10319,11 +10381,11 @@
       <c r="CU72" s="9"/>
       <c r="CV72" s="9"/>
       <c r="CW72" s="9"/>
-      <c r="CX72" s="8"/>
+      <c r="CX72" s="9"/>
       <c r="CY72" s="8"/>
       <c r="CZ72" s="8"/>
       <c r="DA72" s="8"/>
-      <c r="DB72" s="9"/>
+      <c r="DB72" s="8"/>
       <c r="DC72" s="9"/>
       <c r="DD72" s="9"/>
       <c r="DE72" s="9"/>
@@ -10367,67 +10429,67 @@
       <c r="A73" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="CX73" s="5"/>
       <c r="CY73" s="5"/>
       <c r="CZ73" s="5"/>
       <c r="DA73" s="5"/>
+      <c r="DB73" s="5"/>
     </row>
     <row r="74" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="CX74" s="5"/>
       <c r="CY74" s="5"/>
       <c r="CZ74" s="5"/>
       <c r="DA74" s="5"/>
+      <c r="DB74" s="5"/>
     </row>
     <row r="75" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="CX75" s="5"/>
       <c r="CY75" s="5"/>
       <c r="CZ75" s="5"/>
       <c r="DA75" s="5"/>
+      <c r="DB75" s="5"/>
     </row>
     <row r="76" spans="1:144" x14ac:dyDescent="0.2">
-      <c r="CX76" s="5"/>
       <c r="CY76" s="5"/>
       <c r="CZ76" s="5"/>
       <c r="DA76" s="5"/>
+      <c r="DB76" s="5"/>
     </row>
     <row r="77" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="CX77" s="5"/>
       <c r="CY77" s="5"/>
       <c r="CZ77" s="5"/>
       <c r="DA77" s="5"/>
+      <c r="DB77" s="5"/>
     </row>
     <row r="78" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="CX78" s="5"/>
       <c r="CY78" s="5"/>
       <c r="CZ78" s="5"/>
       <c r="DA78" s="5"/>
+      <c r="DB78" s="5"/>
     </row>
     <row r="79" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="CX79" s="5"/>
       <c r="CY79" s="5"/>
       <c r="CZ79" s="5"/>
       <c r="DA79" s="5"/>
+      <c r="DB79" s="5"/>
     </row>
     <row r="80" spans="1:144" x14ac:dyDescent="0.2">
-      <c r="CX80" s="5"/>
       <c r="CY80" s="5"/>
       <c r="CZ80" s="5"/>
       <c r="DA80" s="5"/>
+      <c r="DB80" s="5"/>
     </row>
     <row r="81" spans="1:152" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="17"/>
@@ -10581,10 +10643,13 @@
       <c r="CU81" s="30"/>
       <c r="CV81" s="30"/>
       <c r="CW81" s="30"/>
-      <c r="CX81" s="31"/>
+      <c r="CX81" s="30" t="s">
+        <v>56</v>
+      </c>
       <c r="CY81" s="31"/>
       <c r="CZ81" s="31"/>
       <c r="DA81" s="31"/>
+      <c r="DB81" s="31"/>
     </row>
     <row r="82" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
@@ -10890,17 +10955,20 @@
       <c r="CW82" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="CX82" s="33"/>
+      <c r="CX82" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="CY82" s="33"/>
       <c r="CZ82" s="33"/>
       <c r="DA82" s="33"/>
+      <c r="DB82" s="33"/>
     </row>
     <row r="83" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="7"/>
-      <c r="CX83" s="5"/>
       <c r="CY83" s="5"/>
       <c r="CZ83" s="5"/>
       <c r="DA83" s="5"/>
+      <c r="DB83" s="5"/>
     </row>
     <row r="84" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
@@ -11206,11 +11274,13 @@
       <c r="CW84" s="21">
         <v>-38.632909084895083</v>
       </c>
-      <c r="CX84" s="22"/>
+      <c r="CX84" s="21">
+        <v>-31.506302263599721</v>
+      </c>
       <c r="CY84" s="22"/>
       <c r="CZ84" s="22"/>
       <c r="DA84" s="22"/>
-      <c r="DB84" s="9"/>
+      <c r="DB84" s="22"/>
       <c r="DC84" s="9"/>
       <c r="DD84" s="9"/>
       <c r="DE84" s="9"/>
@@ -11554,11 +11624,13 @@
       <c r="CW85" s="21">
         <v>16.844703243992456</v>
       </c>
-      <c r="CX85" s="22"/>
+      <c r="CX85" s="21">
+        <v>5.292407264612379</v>
+      </c>
       <c r="CY85" s="22"/>
       <c r="CZ85" s="22"/>
       <c r="DA85" s="22"/>
-      <c r="DB85" s="9"/>
+      <c r="DB85" s="22"/>
       <c r="DC85" s="9"/>
       <c r="DD85" s="9"/>
       <c r="DE85" s="9"/>
@@ -11902,11 +11974,13 @@
       <c r="CW86" s="21">
         <v>0.44062460277480398</v>
       </c>
-      <c r="CX86" s="22"/>
+      <c r="CX86" s="21">
+        <v>3.6257847003271308</v>
+      </c>
       <c r="CY86" s="22"/>
       <c r="CZ86" s="22"/>
       <c r="DA86" s="22"/>
-      <c r="DB86" s="9"/>
+      <c r="DB86" s="22"/>
       <c r="DC86" s="9"/>
       <c r="DD86" s="9"/>
       <c r="DE86" s="9"/>
@@ -12047,11 +12121,11 @@
       <c r="CU87" s="23"/>
       <c r="CV87" s="23"/>
       <c r="CW87" s="23"/>
-      <c r="CX87" s="24"/>
+      <c r="CX87" s="23"/>
       <c r="CY87" s="24"/>
       <c r="CZ87" s="24"/>
       <c r="DA87" s="24"/>
-      <c r="DB87" s="9"/>
+      <c r="DB87" s="24"/>
       <c r="DC87" s="9"/>
       <c r="DD87" s="9"/>
       <c r="DE87" s="9"/>
@@ -12395,11 +12469,13 @@
       <c r="CW88" s="21">
         <v>-9.1788156823042044</v>
       </c>
-      <c r="CX88" s="22"/>
+      <c r="CX88" s="21">
+        <v>-4.519646576880973</v>
+      </c>
       <c r="CY88" s="22"/>
       <c r="CZ88" s="22"/>
       <c r="DA88" s="22"/>
-      <c r="DB88" s="9"/>
+      <c r="DB88" s="22"/>
       <c r="DC88" s="9"/>
       <c r="DD88" s="9"/>
       <c r="DE88" s="9"/>
@@ -12541,10 +12617,11 @@
       <c r="CU89" s="26"/>
       <c r="CV89" s="26"/>
       <c r="CW89" s="26"/>
-      <c r="CX89" s="27"/>
+      <c r="CX89" s="26"/>
       <c r="CY89" s="27"/>
       <c r="CZ89" s="27"/>
       <c r="DA89" s="27"/>
+      <c r="DB89" s="27"/>
     </row>
     <row r="90" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A90" s="11"/>
@@ -12648,11 +12725,11 @@
       <c r="CU90" s="21"/>
       <c r="CV90" s="21"/>
       <c r="CW90" s="21"/>
-      <c r="CX90" s="22"/>
+      <c r="CX90" s="21"/>
       <c r="CY90" s="22"/>
       <c r="CZ90" s="22"/>
       <c r="DA90" s="22"/>
-      <c r="DB90" s="9"/>
+      <c r="DB90" s="22"/>
       <c r="DC90" s="9"/>
       <c r="DD90" s="9"/>
       <c r="DE90" s="9"/>
@@ -12996,11 +13073,13 @@
       <c r="CW91" s="21">
         <v>-6.0338827846476875</v>
       </c>
-      <c r="CX91" s="22"/>
+      <c r="CX91" s="21">
+        <v>-2.8163851498245123</v>
+      </c>
       <c r="CY91" s="22"/>
       <c r="CZ91" s="22"/>
       <c r="DA91" s="22"/>
-      <c r="DB91" s="9"/>
+      <c r="DB91" s="22"/>
       <c r="DC91" s="9"/>
       <c r="DD91" s="9"/>
       <c r="DE91" s="9"/>
@@ -13142,19 +13221,20 @@
       <c r="CU92" s="13"/>
       <c r="CV92" s="13"/>
       <c r="CW92" s="13"/>
-      <c r="CX92" s="33"/>
+      <c r="CX92" s="13"/>
       <c r="CY92" s="33"/>
       <c r="CZ92" s="33"/>
       <c r="DA92" s="33"/>
+      <c r="DB92" s="33"/>
     </row>
     <row r="93" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A93" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="CX93" s="5"/>
       <c r="CY93" s="5"/>
       <c r="CZ93" s="5"/>
       <c r="DA93" s="5"/>
+      <c r="DB93" s="5"/>
     </row>
     <row r="94" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A94" s="14" t="s">
@@ -13164,6 +13244,7 @@
       <c r="CY94" s="5"/>
       <c r="CZ94" s="5"/>
       <c r="DA94" s="5"/>
+      <c r="DB94" s="5"/>
     </row>
     <row r="95" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B95" s="9"/>
@@ -13270,7 +13351,7 @@
       <c r="CY95" s="8"/>
       <c r="CZ95" s="8"/>
       <c r="DA95" s="8"/>
-      <c r="DB95" s="9"/>
+      <c r="DB95" s="8"/>
       <c r="DC95" s="9"/>
       <c r="DD95" s="9"/>
       <c r="DE95" s="9"/>
@@ -13658,6 +13739,9 @@
       <c r="CY104" s="30"/>
       <c r="CZ104" s="30"/>
       <c r="DA104" s="30"/>
+      <c r="DB104" s="30">
+        <v>2026</v>
+      </c>
     </row>
     <row r="105" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A105" s="6" t="s">
@@ -13974,6 +14058,9 @@
       </c>
       <c r="DA105" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB105" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -14295,7 +14382,9 @@
       <c r="DA107" s="29">
         <v>117.75852675386741</v>
       </c>
-      <c r="DB107" s="9"/>
+      <c r="DB107" s="29">
+        <v>129.95180880969659</v>
+      </c>
       <c r="DC107" s="9"/>
       <c r="DD107" s="9"/>
       <c r="DE107" s="9"/>
@@ -14659,7 +14748,9 @@
       <c r="DA108" s="29">
         <v>121.20017822819085</v>
       </c>
-      <c r="DB108" s="9"/>
+      <c r="DB108" s="29">
+        <v>117.7196426002636</v>
+      </c>
       <c r="DC108" s="9"/>
       <c r="DD108" s="9"/>
       <c r="DE108" s="9"/>
@@ -15023,7 +15114,9 @@
       <c r="DA109" s="29">
         <v>108.30139280382878</v>
       </c>
-      <c r="DB109" s="9"/>
+      <c r="DB109" s="29">
+        <v>132.37642402911388</v>
+      </c>
       <c r="DC109" s="9"/>
       <c r="DD109" s="9"/>
       <c r="DE109" s="9"/>
@@ -15540,7 +15633,9 @@
       <c r="DA111" s="29">
         <v>115.34860073887199</v>
       </c>
-      <c r="DB111" s="9"/>
+      <c r="DB111" s="29">
+        <v>124.8753027357419</v>
+      </c>
       <c r="DC111" s="9"/>
       <c r="DD111" s="9"/>
       <c r="DE111" s="9"/>
@@ -15694,6 +15789,7 @@
       <c r="CY112" s="18"/>
       <c r="CZ112" s="18"/>
       <c r="DA112" s="18"/>
+      <c r="DB112" s="18"/>
     </row>
     <row r="113" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A113" s="11"/>
@@ -15801,7 +15897,7 @@
       <c r="CY113" s="3"/>
       <c r="CZ113" s="3"/>
       <c r="DA113" s="3"/>
-      <c r="DB113" s="9"/>
+      <c r="DB113" s="3"/>
       <c r="DC113" s="9"/>
       <c r="DD113" s="9"/>
       <c r="DE113" s="9"/>
@@ -16165,7 +16261,9 @@
       <c r="DA114" s="29">
         <v>114.9509895048661</v>
       </c>
-      <c r="DB114" s="9"/>
+      <c r="DB114" s="29">
+        <v>125.71206497482225</v>
+      </c>
       <c r="DC114" s="9"/>
       <c r="DD114" s="9"/>
       <c r="DE114" s="9"/>
@@ -16319,6 +16417,7 @@
       <c r="CY115" s="13"/>
       <c r="CZ115" s="13"/>
       <c r="DA115" s="13"/>
+      <c r="DB115" s="13"/>
     </row>
     <row r="116" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A116" s="19" t="s">
@@ -16518,6 +16617,9 @@
       <c r="CY128" s="30"/>
       <c r="CZ128" s="30"/>
       <c r="DA128" s="30"/>
+      <c r="DB128" s="30">
+        <v>2026</v>
+      </c>
     </row>
     <row r="129" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
@@ -16834,6 +16936,9 @@
       </c>
       <c r="DA129" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB129" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17155,7 +17260,9 @@
       <c r="DA131" s="29">
         <v>25.205734832062269</v>
       </c>
-      <c r="DB131" s="9"/>
+      <c r="DB131" s="29">
+        <v>18.855507337013471</v>
+      </c>
       <c r="DC131" s="9"/>
       <c r="DD131" s="9"/>
       <c r="DE131" s="9"/>
@@ -17519,7 +17626,9 @@
       <c r="DA132" s="29">
         <v>38.385793908998608</v>
       </c>
-      <c r="DB132" s="9"/>
+      <c r="DB132" s="29">
+        <v>45.420260124929676</v>
+      </c>
       <c r="DC132" s="9"/>
       <c r="DD132" s="9"/>
       <c r="DE132" s="9"/>
@@ -17883,7 +17992,9 @@
       <c r="DA133" s="29">
         <v>36.408471258939116</v>
       </c>
-      <c r="DB133" s="9"/>
+      <c r="DB133" s="29">
+        <v>35.724232538056846</v>
+      </c>
       <c r="DC133" s="9"/>
       <c r="DD133" s="9"/>
       <c r="DE133" s="9"/>
@@ -18400,7 +18511,9 @@
       <c r="DA135" s="29">
         <v>100</v>
       </c>
-      <c r="DB135" s="9"/>
+      <c r="DB135" s="29">
+        <v>100</v>
+      </c>
       <c r="DC135" s="9"/>
       <c r="DD135" s="9"/>
       <c r="DE135" s="9"/>
@@ -18554,6 +18667,7 @@
       <c r="CY136" s="18"/>
       <c r="CZ136" s="18"/>
       <c r="DA136" s="18"/>
+      <c r="DB136" s="18"/>
     </row>
     <row r="137" spans="1:152" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="11"/>
@@ -18661,7 +18775,7 @@
       <c r="CY137" s="3"/>
       <c r="CZ137" s="3"/>
       <c r="DA137" s="3"/>
-      <c r="DB137" s="9"/>
+      <c r="DB137" s="3"/>
       <c r="DC137" s="9"/>
       <c r="DD137" s="9"/>
       <c r="DE137" s="9"/>
@@ -18815,7 +18929,7 @@
       <c r="CY138" s="3"/>
       <c r="CZ138" s="3"/>
       <c r="DA138" s="3"/>
-      <c r="DB138" s="9"/>
+      <c r="DB138" s="3"/>
       <c r="DC138" s="9"/>
       <c r="DD138" s="9"/>
       <c r="DE138" s="9"/>
@@ -18969,6 +19083,7 @@
       <c r="CY139" s="13"/>
       <c r="CZ139" s="13"/>
       <c r="DA139" s="13"/>
+      <c r="DB139" s="13"/>
     </row>
     <row r="140" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A140" s="19" t="s">
@@ -19474,6 +19589,9 @@
       <c r="CY152" s="30"/>
       <c r="CZ152" s="30"/>
       <c r="DA152" s="30"/>
+      <c r="DB152" s="30">
+        <v>2026</v>
+      </c>
     </row>
     <row r="153" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A153" s="6" t="s">
@@ -19790,6 +19908,9 @@
       </c>
       <c r="DA153" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB153" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20111,7 +20232,9 @@
       <c r="DA155" s="29">
         <v>24.689899947121607</v>
       </c>
-      <c r="DB155" s="9"/>
+      <c r="DB155" s="29">
+        <v>18.118925842684138</v>
+      </c>
       <c r="DC155" s="9"/>
       <c r="DD155" s="9"/>
       <c r="DE155" s="9"/>
@@ -20475,7 +20598,9 @@
       <c r="DA156" s="29">
         <v>36.532517364102532</v>
       </c>
-      <c r="DB156" s="9"/>
+      <c r="DB156" s="29">
+        <v>48.181158285508083</v>
+      </c>
       <c r="DC156" s="9"/>
       <c r="DD156" s="9"/>
       <c r="DE156" s="9"/>
@@ -20839,7 +20964,9 @@
       <c r="DA157" s="29">
         <v>38.777582688775844</v>
       </c>
-      <c r="DB157" s="9"/>
+      <c r="DB157" s="29">
+        <v>33.699915871807768</v>
+      </c>
       <c r="DC157" s="9"/>
       <c r="DD157" s="9"/>
       <c r="DE157" s="9"/>
@@ -21356,7 +21483,9 @@
       <c r="DA159" s="29">
         <v>100</v>
       </c>
-      <c r="DB159" s="9"/>
+      <c r="DB159" s="29">
+        <v>100</v>
+      </c>
       <c r="DC159" s="9"/>
       <c r="DD159" s="9"/>
       <c r="DE159" s="9"/>
@@ -21510,6 +21639,7 @@
       <c r="CY160" s="18"/>
       <c r="CZ160" s="18"/>
       <c r="DA160" s="18"/>
+      <c r="DB160" s="18"/>
     </row>
     <row r="161" spans="1:152" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="11"/>
@@ -21617,7 +21747,7 @@
       <c r="CY161" s="3"/>
       <c r="CZ161" s="3"/>
       <c r="DA161" s="3"/>
-      <c r="DB161" s="9"/>
+      <c r="DB161" s="3"/>
       <c r="DC161" s="9"/>
       <c r="DD161" s="9"/>
       <c r="DE161" s="9"/>
@@ -21771,7 +21901,7 @@
       <c r="CY162" s="3"/>
       <c r="CZ162" s="3"/>
       <c r="DA162" s="3"/>
-      <c r="DB162" s="9"/>
+      <c r="DB162" s="3"/>
       <c r="DC162" s="9"/>
       <c r="DD162" s="9"/>
       <c r="DE162" s="9"/>
@@ -21925,6 +22055,7 @@
       <c r="CY163" s="13"/>
       <c r="CZ163" s="13"/>
       <c r="DA163" s="13"/>
+      <c r="DB163" s="13"/>
     </row>
     <row r="164" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A164" s="19" t="s">
@@ -21939,12 +22070,14 @@
       <c r="CY165" s="5"/>
       <c r="CZ165" s="5"/>
       <c r="DA165" s="5"/>
+      <c r="DB165" s="5"/>
     </row>
     <row r="166" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CX166" s="5"/>
       <c r="CY166" s="5"/>
       <c r="CZ166" s="5"/>
       <c r="DA166" s="5"/>
+      <c r="DB166" s="5"/>
     </row>
     <row r="167" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT167" s="7"/>
@@ -21954,6 +22087,7 @@
       <c r="CY167" s="7"/>
       <c r="CZ167" s="7"/>
       <c r="DA167" s="7"/>
+      <c r="DB167" s="7"/>
     </row>
     <row r="168" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT168" s="7"/>
@@ -21963,6 +22097,7 @@
       <c r="CY168" s="7"/>
       <c r="CZ168" s="7"/>
       <c r="DA168" s="7"/>
+      <c r="DB168" s="7"/>
     </row>
     <row r="169" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT169" s="7"/>
@@ -21972,6 +22107,7 @@
       <c r="CY169" s="7"/>
       <c r="CZ169" s="7"/>
       <c r="DA169" s="7"/>
+      <c r="DB169" s="7"/>
     </row>
     <row r="170" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT170" s="7"/>
@@ -21981,6 +22117,7 @@
       <c r="CY170" s="7"/>
       <c r="CZ170" s="7"/>
       <c r="DA170" s="7"/>
+      <c r="DB170" s="7"/>
     </row>
     <row r="171" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT171" s="7"/>
@@ -21990,6 +22127,7 @@
       <c r="CY171" s="7"/>
       <c r="CZ171" s="7"/>
       <c r="DA171" s="7"/>
+      <c r="DB171" s="7"/>
     </row>
     <row r="172" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT172" s="7"/>
@@ -21999,6 +22137,13 @@
       <c r="CY172" s="7"/>
       <c r="CZ172" s="7"/>
       <c r="DA172" s="7"/>
+      <c r="DB172" s="7"/>
+    </row>
+    <row r="173" spans="1:152" x14ac:dyDescent="0.2">
+      <c r="DB173" s="7"/>
+    </row>
+    <row r="174" spans="1:152" x14ac:dyDescent="0.2">
+      <c r="DB174" s="7"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -22006,9 +22151,9 @@
   <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="48" max="81" man="1"/>
-    <brk id="96" max="81" man="1"/>
-    <brk id="119" max="81" man="1"/>
+    <brk id="48" max="105" man="1"/>
+    <brk id="96" max="105" man="1"/>
+    <brk id="119" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-12CNS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-12CNS_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918DEB39-D235-4C5E-BC56-C4F64EFCE102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926ED5EB-ECBA-45BA-B2E8-751BB402A490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -359,7 +359,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">CNS!$A$1:$DB$165</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">CNS!$A$1:$DC$165</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -533,7 +533,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="57">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -697,13 +697,13 @@
     <t>Percent Share to the Institutional Sector At Constant 2018 Prices</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>As of August 2026</t>
   </si>
 </sst>
 </file>
@@ -1227,12 +1227,12 @@
   <sheetPr transitionEvaluation="1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:EV174"/>
+  <dimension ref="A1:EV172"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="49.140625" style="4" customWidth="1"/>
-    <col min="2" max="106" width="13" style="4" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="4"/>
+    <col min="2" max="107" width="13" style="4" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:152" x14ac:dyDescent="0.2">
@@ -1247,7 +1247,7 @@
     </row>
     <row r="3" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:152" x14ac:dyDescent="0.2">
@@ -1257,7 +1257,7 @@
     </row>
     <row r="6" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:152" x14ac:dyDescent="0.2">
@@ -1426,6 +1426,7 @@
       <c r="DB9" s="30">
         <v>2026</v>
       </c>
+      <c r="DC9" s="30"/>
     </row>
     <row r="10" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
@@ -1745,6 +1746,9 @@
       </c>
       <c r="DB10" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2069,7 +2073,9 @@
       <c r="DB12" s="10">
         <v>159081.32174658342</v>
       </c>
-      <c r="DC12" s="9"/>
+      <c r="DC12" s="10">
+        <v>450642.57663276489</v>
+      </c>
       <c r="DD12" s="9"/>
       <c r="DE12" s="9"/>
       <c r="DF12" s="9"/>
@@ -2433,9 +2439,11 @@
         <v>354288.92856924684</v>
       </c>
       <c r="DB13" s="10">
-        <v>383204.48692269996</v>
-      </c>
-      <c r="DC13" s="9"/>
+        <v>383423.70264801965</v>
+      </c>
+      <c r="DC13" s="10">
+        <v>395891.05755576806</v>
+      </c>
       <c r="DD13" s="9"/>
       <c r="DE13" s="9"/>
       <c r="DF13" s="9"/>
@@ -2799,9 +2807,11 @@
         <v>336038.85603496339</v>
       </c>
       <c r="DB14" s="10">
-        <v>301400.43590238004</v>
-      </c>
-      <c r="DC14" s="9"/>
+        <v>303823.75903050153</v>
+      </c>
+      <c r="DC14" s="10">
+        <v>304735.50416024303</v>
+      </c>
       <c r="DD14" s="9"/>
       <c r="DE14" s="9"/>
       <c r="DF14" s="9"/>
@@ -3318,9 +3328,11 @@
         <v>922968.87074723886</v>
       </c>
       <c r="DB16" s="3">
-        <v>843686.24457166344</v>
-      </c>
-      <c r="DC16" s="9"/>
+        <v>846328.78342510457</v>
+      </c>
+      <c r="DC16" s="3">
+        <v>1151269.1383487759</v>
+      </c>
       <c r="DD16" s="9"/>
       <c r="DE16" s="9"/>
       <c r="DF16" s="9"/>
@@ -3474,6 +3486,7 @@
       <c r="CZ17" s="18"/>
       <c r="DA17" s="18"/>
       <c r="DB17" s="18"/>
+      <c r="DC17" s="18"/>
     </row>
     <row r="18" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A18" s="11"/>
@@ -3582,7 +3595,7 @@
       <c r="CZ18" s="3"/>
       <c r="DA18" s="3"/>
       <c r="DB18" s="3"/>
-      <c r="DC18" s="9"/>
+      <c r="DC18" s="3"/>
       <c r="DD18" s="9"/>
       <c r="DE18" s="9"/>
       <c r="DF18" s="9"/>
@@ -3946,9 +3959,11 @@
         <v>520090.39122897363</v>
       </c>
       <c r="DB19" s="10">
-        <v>395509.7327156323</v>
-      </c>
-      <c r="DC19" s="9"/>
+        <v>396402.98150470387</v>
+      </c>
+      <c r="DC19" s="10">
+        <v>608235.97546892019</v>
+      </c>
       <c r="DD19" s="9"/>
       <c r="DE19" s="9"/>
       <c r="DF19" s="9"/>
@@ -4102,6 +4117,7 @@
       <c r="CZ20" s="13"/>
       <c r="DA20" s="13"/>
       <c r="DB20" s="13"/>
+      <c r="DC20" s="13"/>
     </row>
     <row r="21" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
@@ -4145,7 +4161,7 @@
     </row>
     <row r="27" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:152" x14ac:dyDescent="0.2">
@@ -4155,7 +4171,7 @@
     </row>
     <row r="30" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:152" x14ac:dyDescent="0.2">
@@ -4324,6 +4340,7 @@
       <c r="DB33" s="30">
         <v>2026</v>
       </c>
+      <c r="DC33" s="30"/>
     </row>
     <row r="34" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
@@ -4643,6 +4660,9 @@
       </c>
       <c r="DB34" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC34" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -4965,9 +4985,11 @@
         <v>197557.7417245399</v>
       </c>
       <c r="DB36" s="10">
-        <v>122415.62714955705</v>
-      </c>
-      <c r="DC36" s="9"/>
+        <v>122374.03028202402</v>
+      </c>
+      <c r="DC36" s="10">
+        <v>360409.20522673667</v>
+      </c>
       <c r="DD36" s="9"/>
       <c r="DE36" s="9"/>
       <c r="DF36" s="9"/>
@@ -5331,9 +5353,11 @@
         <v>292317.16796835547</v>
       </c>
       <c r="DB37" s="10">
-        <v>325522.97854312538</v>
-      </c>
-      <c r="DC37" s="9"/>
+        <v>325618.79195993039</v>
+      </c>
+      <c r="DC37" s="10">
+        <v>321068.34160715371</v>
+      </c>
       <c r="DD37" s="9"/>
       <c r="DE37" s="9"/>
       <c r="DF37" s="9"/>
@@ -5697,9 +5721,11 @@
         <v>310281.19522308063</v>
       </c>
       <c r="DB38" s="10">
-        <v>227684.37666520762</v>
-      </c>
-      <c r="DC38" s="9"/>
+        <v>229455.4533748455</v>
+      </c>
+      <c r="DC38" s="10">
+        <v>238095.26508493925</v>
+      </c>
       <c r="DD38" s="9"/>
       <c r="DE38" s="9"/>
       <c r="DF38" s="9"/>
@@ -6216,9 +6242,11 @@
         <v>800156.10491597606</v>
       </c>
       <c r="DB40" s="3">
-        <v>675622.98235789011</v>
-      </c>
-      <c r="DC40" s="9"/>
+        <v>677448.27561679995</v>
+      </c>
+      <c r="DC40" s="3">
+        <v>919572.81191882957</v>
+      </c>
       <c r="DD40" s="9"/>
       <c r="DE40" s="9"/>
       <c r="DF40" s="9"/>
@@ -6372,6 +6400,7 @@
       <c r="CZ41" s="18"/>
       <c r="DA41" s="18"/>
       <c r="DB41" s="18"/>
+      <c r="DC41" s="18"/>
     </row>
     <row r="42" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A42" s="11"/>
@@ -6480,7 +6509,7 @@
       <c r="CZ42" s="3"/>
       <c r="DA42" s="3"/>
       <c r="DB42" s="3"/>
-      <c r="DC42" s="9"/>
+      <c r="DC42" s="3"/>
       <c r="DD42" s="9"/>
       <c r="DE42" s="9"/>
       <c r="DF42" s="9"/>
@@ -6844,9 +6873,11 @@
         <v>452445.3364596371</v>
       </c>
       <c r="DB43" s="10">
-        <v>314615.57233575423</v>
-      </c>
-      <c r="DC43" s="9"/>
+        <v>315068.61507614731</v>
+      </c>
+      <c r="DC43" s="10">
+        <v>432418.511810583</v>
+      </c>
       <c r="DD43" s="9"/>
       <c r="DE43" s="9"/>
       <c r="DF43" s="9"/>
@@ -7000,6 +7031,7 @@
       <c r="CZ44" s="13"/>
       <c r="DA44" s="13"/>
       <c r="DB44" s="13"/>
+      <c r="DC44" s="13"/>
     </row>
     <row r="45" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A45" s="19" t="s">
@@ -7329,7 +7361,7 @@
     </row>
     <row r="51" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:144" x14ac:dyDescent="0.2">
@@ -7339,6 +7371,7 @@
       <c r="CZ52" s="5"/>
       <c r="DA52" s="5"/>
       <c r="DB52" s="5"/>
+      <c r="DC52" s="5"/>
     </row>
     <row r="53" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
@@ -7352,16 +7385,18 @@
       <c r="CZ53" s="5"/>
       <c r="DA53" s="5"/>
       <c r="DB53" s="5"/>
+      <c r="DC53" s="5"/>
     </row>
     <row r="54" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="CX54" s="5"/>
       <c r="CY54" s="5"/>
       <c r="CZ54" s="5"/>
       <c r="DA54" s="5"/>
       <c r="DB54" s="5"/>
+      <c r="DC54" s="5"/>
     </row>
     <row r="55" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
@@ -7372,13 +7407,13 @@
       <c r="CZ55" s="5"/>
       <c r="DA55" s="5"/>
       <c r="DB55" s="5"/>
+      <c r="DC55" s="5"/>
     </row>
     <row r="56" spans="1:144" x14ac:dyDescent="0.2">
-      <c r="CX56" s="5"/>
-      <c r="CY56" s="5"/>
       <c r="CZ56" s="5"/>
       <c r="DA56" s="5"/>
       <c r="DB56" s="5"/>
+      <c r="DC56" s="5"/>
     </row>
     <row r="57" spans="1:144" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17"/>
@@ -7533,12 +7568,13 @@
       <c r="CV57" s="30"/>
       <c r="CW57" s="30"/>
       <c r="CX57" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="CY57" s="31"/>
+        <v>54</v>
+      </c>
+      <c r="CY57" s="30"/>
       <c r="CZ57" s="31"/>
       <c r="DA57" s="31"/>
       <c r="DB57" s="31"/>
+      <c r="DC57" s="31"/>
     </row>
     <row r="58" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
@@ -7847,17 +7883,20 @@
       <c r="CX58" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="CY58" s="32"/>
+      <c r="CY58" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ58" s="32"/>
       <c r="DA58" s="32"/>
       <c r="DB58" s="32"/>
+      <c r="DC58" s="32"/>
     </row>
     <row r="59" spans="1:144" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7"/>
-      <c r="CY59" s="5"/>
       <c r="CZ59" s="5"/>
       <c r="DA59" s="5"/>
       <c r="DB59" s="5"/>
+      <c r="DC59" s="5"/>
     </row>
     <row r="60" spans="1:144" s="25" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
@@ -8166,11 +8205,13 @@
       <c r="CX60" s="21">
         <v>-29.78456317431187</v>
       </c>
-      <c r="CY60" s="22"/>
+      <c r="CY60" s="21">
+        <v>-30.339481375611115</v>
+      </c>
       <c r="CZ60" s="22"/>
       <c r="DA60" s="22"/>
       <c r="DB60" s="22"/>
-      <c r="DC60" s="23"/>
+      <c r="DC60" s="22"/>
       <c r="DD60" s="23"/>
       <c r="DE60" s="23"/>
       <c r="DF60" s="23"/>
@@ -8514,13 +8555,15 @@
         <v>16.957478004499379</v>
       </c>
       <c r="CX61" s="21">
-        <v>7.4737189737454912</v>
-      </c>
-      <c r="CY61" s="22"/>
+        <v>7.5352003239427034</v>
+      </c>
+      <c r="CY61" s="21">
+        <v>8.4368301622409092</v>
+      </c>
       <c r="CZ61" s="22"/>
       <c r="DA61" s="22"/>
       <c r="DB61" s="22"/>
-      <c r="DC61" s="23"/>
+      <c r="DC61" s="22"/>
       <c r="DD61" s="23"/>
       <c r="DE61" s="23"/>
       <c r="DF61" s="23"/>
@@ -8864,13 +8907,15 @@
         <v>1.6535035828119362</v>
       </c>
       <c r="CX62" s="21">
-        <v>5.781591509267983</v>
-      </c>
-      <c r="CY62" s="22"/>
+        <v>6.632097834736399</v>
+      </c>
+      <c r="CY62" s="21">
+        <v>2.9806669638986705</v>
+      </c>
       <c r="CZ62" s="22"/>
       <c r="DA62" s="22"/>
       <c r="DB62" s="22"/>
-      <c r="DC62" s="23"/>
+      <c r="DC62" s="22"/>
       <c r="DD62" s="23"/>
       <c r="DE62" s="23"/>
       <c r="DF62" s="23"/>
@@ -9012,11 +9057,11 @@
       <c r="CV63" s="23"/>
       <c r="CW63" s="23"/>
       <c r="CX63" s="23"/>
-      <c r="CY63" s="24"/>
+      <c r="CY63" s="23"/>
       <c r="CZ63" s="24"/>
       <c r="DA63" s="24"/>
       <c r="DB63" s="24"/>
-      <c r="DC63" s="23"/>
+      <c r="DC63" s="24"/>
       <c r="DD63" s="23"/>
       <c r="DE63" s="23"/>
       <c r="DF63" s="23"/>
@@ -9360,13 +9405,15 @@
         <v>-8.3326253751103536</v>
       </c>
       <c r="CX64" s="21">
-        <v>-2.8061988310239769</v>
-      </c>
-      <c r="CY64" s="22"/>
+        <v>-2.5017747663255534</v>
+      </c>
+      <c r="CY64" s="21">
+        <v>-11.976884647349635</v>
+      </c>
       <c r="CZ64" s="22"/>
       <c r="DA64" s="22"/>
       <c r="DB64" s="22"/>
-      <c r="DC64" s="23"/>
+      <c r="DC64" s="22"/>
       <c r="DD64" s="23"/>
       <c r="DE64" s="23"/>
       <c r="DF64" s="23"/>
@@ -9508,10 +9555,11 @@
       <c r="CV65" s="26"/>
       <c r="CW65" s="26"/>
       <c r="CX65" s="26"/>
-      <c r="CY65" s="27"/>
+      <c r="CY65" s="26"/>
       <c r="CZ65" s="27"/>
       <c r="DA65" s="27"/>
       <c r="DB65" s="27"/>
+      <c r="DC65" s="27"/>
     </row>
     <row r="66" spans="1:144" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="11"/>
@@ -9616,11 +9664,11 @@
       <c r="CV66" s="21"/>
       <c r="CW66" s="21"/>
       <c r="CX66" s="21"/>
-      <c r="CY66" s="22"/>
+      <c r="CY66" s="21"/>
       <c r="CZ66" s="22"/>
       <c r="DA66" s="22"/>
       <c r="DB66" s="22"/>
-      <c r="DC66" s="23"/>
+      <c r="DC66" s="22"/>
       <c r="DD66" s="23"/>
       <c r="DE66" s="23"/>
       <c r="DF66" s="23"/>
@@ -9964,13 +10012,15 @@
         <v>-5.6429241925776381</v>
       </c>
       <c r="CX67" s="21">
-        <v>-0.82243781382128134</v>
-      </c>
-      <c r="CY67" s="22"/>
+        <v>-0.5984477827350787</v>
+      </c>
+      <c r="CY67" s="21">
+        <v>-10.708186349298671</v>
+      </c>
       <c r="CZ67" s="22"/>
       <c r="DA67" s="22"/>
       <c r="DB67" s="22"/>
-      <c r="DC67" s="23"/>
+      <c r="DC67" s="22"/>
       <c r="DD67" s="23"/>
       <c r="DE67" s="23"/>
       <c r="DF67" s="23"/>
@@ -10112,28 +10162,29 @@
       <c r="CV68" s="13"/>
       <c r="CW68" s="13"/>
       <c r="CX68" s="13"/>
-      <c r="CY68" s="33"/>
+      <c r="CY68" s="13"/>
       <c r="CZ68" s="33"/>
       <c r="DA68" s="33"/>
       <c r="DB68" s="33"/>
+      <c r="DC68" s="33"/>
     </row>
     <row r="69" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A69" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="CY69" s="5"/>
       <c r="CZ69" s="5"/>
       <c r="DA69" s="5"/>
       <c r="DB69" s="5"/>
+      <c r="DC69" s="5"/>
     </row>
     <row r="70" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A70" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="CY70" s="5"/>
       <c r="CZ70" s="5"/>
       <c r="DA70" s="5"/>
       <c r="DB70" s="5"/>
+      <c r="DC70" s="5"/>
     </row>
     <row r="71" spans="1:144" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B71" s="9"/>
@@ -10237,11 +10288,11 @@
       <c r="CV71" s="9"/>
       <c r="CW71" s="9"/>
       <c r="CX71" s="9"/>
-      <c r="CY71" s="8"/>
+      <c r="CY71" s="9"/>
       <c r="CZ71" s="8"/>
       <c r="DA71" s="8"/>
       <c r="DB71" s="8"/>
-      <c r="DC71" s="9"/>
+      <c r="DC71" s="8"/>
       <c r="DD71" s="9"/>
       <c r="DE71" s="9"/>
       <c r="DF71" s="9"/>
@@ -10382,11 +10433,11 @@
       <c r="CV72" s="9"/>
       <c r="CW72" s="9"/>
       <c r="CX72" s="9"/>
-      <c r="CY72" s="8"/>
+      <c r="CY72" s="9"/>
       <c r="CZ72" s="8"/>
       <c r="DA72" s="8"/>
       <c r="DB72" s="8"/>
-      <c r="DC72" s="9"/>
+      <c r="DC72" s="8"/>
       <c r="DD72" s="9"/>
       <c r="DE72" s="9"/>
       <c r="DF72" s="9"/>
@@ -10429,67 +10480,67 @@
       <c r="A73" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="CY73" s="5"/>
       <c r="CZ73" s="5"/>
       <c r="DA73" s="5"/>
       <c r="DB73" s="5"/>
+      <c r="DC73" s="5"/>
     </row>
     <row r="74" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="CY74" s="5"/>
       <c r="CZ74" s="5"/>
       <c r="DA74" s="5"/>
       <c r="DB74" s="5"/>
+      <c r="DC74" s="5"/>
     </row>
     <row r="75" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="CY75" s="5"/>
+        <v>56</v>
+      </c>
       <c r="CZ75" s="5"/>
       <c r="DA75" s="5"/>
       <c r="DB75" s="5"/>
+      <c r="DC75" s="5"/>
     </row>
     <row r="76" spans="1:144" x14ac:dyDescent="0.2">
-      <c r="CY76" s="5"/>
       <c r="CZ76" s="5"/>
       <c r="DA76" s="5"/>
       <c r="DB76" s="5"/>
+      <c r="DC76" s="5"/>
     </row>
     <row r="77" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="CY77" s="5"/>
       <c r="CZ77" s="5"/>
       <c r="DA77" s="5"/>
       <c r="DB77" s="5"/>
+      <c r="DC77" s="5"/>
     </row>
     <row r="78" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="CY78" s="5"/>
+        <v>55</v>
+      </c>
       <c r="CZ78" s="5"/>
       <c r="DA78" s="5"/>
       <c r="DB78" s="5"/>
+      <c r="DC78" s="5"/>
     </row>
     <row r="79" spans="1:144" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="CY79" s="5"/>
       <c r="CZ79" s="5"/>
       <c r="DA79" s="5"/>
       <c r="DB79" s="5"/>
+      <c r="DC79" s="5"/>
     </row>
     <row r="80" spans="1:144" x14ac:dyDescent="0.2">
-      <c r="CY80" s="5"/>
       <c r="CZ80" s="5"/>
       <c r="DA80" s="5"/>
       <c r="DB80" s="5"/>
+      <c r="DC80" s="5"/>
     </row>
     <row r="81" spans="1:152" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="17"/>
@@ -10644,12 +10695,13 @@
       <c r="CV81" s="30"/>
       <c r="CW81" s="30"/>
       <c r="CX81" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="CY81" s="31"/>
+        <v>54</v>
+      </c>
+      <c r="CY81" s="30"/>
       <c r="CZ81" s="31"/>
       <c r="DA81" s="31"/>
       <c r="DB81" s="31"/>
+      <c r="DC81" s="31"/>
     </row>
     <row r="82" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
@@ -10958,17 +11010,20 @@
       <c r="CX82" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="CY82" s="33"/>
+      <c r="CY82" s="15" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ82" s="33"/>
       <c r="DA82" s="33"/>
       <c r="DB82" s="33"/>
+      <c r="DC82" s="33"/>
     </row>
     <row r="83" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="7"/>
-      <c r="CY83" s="5"/>
       <c r="CZ83" s="5"/>
       <c r="DA83" s="5"/>
       <c r="DB83" s="5"/>
+      <c r="DC83" s="5"/>
     </row>
     <row r="84" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
@@ -11275,13 +11330,15 @@
         <v>-38.632909084895083</v>
       </c>
       <c r="CX84" s="21">
-        <v>-31.506302263599721</v>
-      </c>
-      <c r="CY84" s="22"/>
+        <v>-31.529576443031957</v>
+      </c>
+      <c r="CY84" s="21">
+        <v>-32.409210781422701</v>
+      </c>
       <c r="CZ84" s="22"/>
       <c r="DA84" s="22"/>
       <c r="DB84" s="22"/>
-      <c r="DC84" s="9"/>
+      <c r="DC84" s="22"/>
       <c r="DD84" s="9"/>
       <c r="DE84" s="9"/>
       <c r="DF84" s="9"/>
@@ -11625,13 +11682,15 @@
         <v>16.844703243992456</v>
       </c>
       <c r="CX85" s="21">
-        <v>5.292407264612379</v>
-      </c>
-      <c r="CY85" s="22"/>
+        <v>5.3233987029089889</v>
+      </c>
+      <c r="CY85" s="21">
+        <v>3.791181601968205</v>
+      </c>
       <c r="CZ85" s="22"/>
       <c r="DA85" s="22"/>
       <c r="DB85" s="22"/>
-      <c r="DC85" s="9"/>
+      <c r="DC85" s="22"/>
       <c r="DD85" s="9"/>
       <c r="DE85" s="9"/>
       <c r="DF85" s="9"/>
@@ -11975,13 +12034,15 @@
         <v>0.44062460277480398</v>
       </c>
       <c r="CX86" s="21">
-        <v>3.6257847003271308</v>
-      </c>
-      <c r="CY86" s="22"/>
+        <v>4.4318532434953966</v>
+      </c>
+      <c r="CY86" s="21">
+        <v>0.76642561811472376</v>
+      </c>
       <c r="CZ86" s="22"/>
       <c r="DA86" s="22"/>
       <c r="DB86" s="22"/>
-      <c r="DC86" s="9"/>
+      <c r="DC86" s="22"/>
       <c r="DD86" s="9"/>
       <c r="DE86" s="9"/>
       <c r="DF86" s="9"/>
@@ -12122,11 +12183,11 @@
       <c r="CV87" s="23"/>
       <c r="CW87" s="23"/>
       <c r="CX87" s="23"/>
-      <c r="CY87" s="24"/>
+      <c r="CY87" s="23"/>
       <c r="CZ87" s="24"/>
       <c r="DA87" s="24"/>
       <c r="DB87" s="24"/>
-      <c r="DC87" s="9"/>
+      <c r="DC87" s="24"/>
       <c r="DD87" s="9"/>
       <c r="DE87" s="9"/>
       <c r="DF87" s="9"/>
@@ -12470,13 +12531,15 @@
         <v>-9.1788156823042044</v>
       </c>
       <c r="CX88" s="21">
-        <v>-4.519646576880973</v>
-      </c>
-      <c r="CY88" s="22"/>
+        <v>-4.2616925847693921</v>
+      </c>
+      <c r="CY88" s="21">
+        <v>-14.763399874615942</v>
+      </c>
       <c r="CZ88" s="22"/>
       <c r="DA88" s="22"/>
       <c r="DB88" s="22"/>
-      <c r="DC88" s="9"/>
+      <c r="DC88" s="22"/>
       <c r="DD88" s="9"/>
       <c r="DE88" s="9"/>
       <c r="DF88" s="9"/>
@@ -12618,10 +12681,11 @@
       <c r="CV89" s="26"/>
       <c r="CW89" s="26"/>
       <c r="CX89" s="26"/>
-      <c r="CY89" s="27"/>
+      <c r="CY89" s="26"/>
       <c r="CZ89" s="27"/>
       <c r="DA89" s="27"/>
       <c r="DB89" s="27"/>
+      <c r="DC89" s="27"/>
     </row>
     <row r="90" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A90" s="11"/>
@@ -12726,11 +12790,11 @@
       <c r="CV90" s="21"/>
       <c r="CW90" s="21"/>
       <c r="CX90" s="21"/>
-      <c r="CY90" s="22"/>
+      <c r="CY90" s="21"/>
       <c r="CZ90" s="22"/>
       <c r="DA90" s="22"/>
       <c r="DB90" s="22"/>
-      <c r="DC90" s="9"/>
+      <c r="DC90" s="22"/>
       <c r="DD90" s="9"/>
       <c r="DE90" s="9"/>
       <c r="DF90" s="9"/>
@@ -13074,13 +13138,15 @@
         <v>-6.0338827846476875</v>
       </c>
       <c r="CX91" s="21">
-        <v>-2.8163851498245123</v>
-      </c>
-      <c r="CY91" s="22"/>
+        <v>-2.6764418823436387</v>
+      </c>
+      <c r="CY91" s="21">
+        <v>-13.90099266257036</v>
+      </c>
       <c r="CZ91" s="22"/>
       <c r="DA91" s="22"/>
       <c r="DB91" s="22"/>
-      <c r="DC91" s="9"/>
+      <c r="DC91" s="22"/>
       <c r="DD91" s="9"/>
       <c r="DE91" s="9"/>
       <c r="DF91" s="9"/>
@@ -13222,10 +13288,11 @@
       <c r="CV92" s="13"/>
       <c r="CW92" s="13"/>
       <c r="CX92" s="13"/>
-      <c r="CY92" s="33"/>
+      <c r="CY92" s="13"/>
       <c r="CZ92" s="33"/>
       <c r="DA92" s="33"/>
       <c r="DB92" s="33"/>
+      <c r="DC92" s="33"/>
     </row>
     <row r="93" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A93" s="19" t="s">
@@ -13235,16 +13302,17 @@
       <c r="CZ93" s="5"/>
       <c r="DA93" s="5"/>
       <c r="DB93" s="5"/>
+      <c r="DC93" s="5"/>
     </row>
     <row r="94" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A94" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="CX94" s="5"/>
       <c r="CY94" s="5"/>
       <c r="CZ94" s="5"/>
       <c r="DA94" s="5"/>
       <c r="DB94" s="5"/>
+      <c r="DC94" s="5"/>
     </row>
     <row r="95" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B95" s="9"/>
@@ -13352,7 +13420,7 @@
       <c r="CZ95" s="8"/>
       <c r="DA95" s="8"/>
       <c r="DB95" s="8"/>
-      <c r="DC95" s="9"/>
+      <c r="DC95" s="8"/>
       <c r="DD95" s="9"/>
       <c r="DE95" s="9"/>
       <c r="DF95" s="9"/>
@@ -13561,7 +13629,7 @@
     </row>
     <row r="98" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="CZ98" s="7"/>
       <c r="DA98" s="7"/>
@@ -13573,7 +13641,7 @@
     </row>
     <row r="101" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102" spans="1:152" x14ac:dyDescent="0.2">
@@ -13742,6 +13810,7 @@
       <c r="DB104" s="30">
         <v>2026</v>
       </c>
+      <c r="DC104" s="30"/>
     </row>
     <row r="105" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A105" s="6" t="s">
@@ -14061,6 +14130,9 @@
       </c>
       <c r="DB105" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC105" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -14383,9 +14455,11 @@
         <v>117.75852675386741</v>
       </c>
       <c r="DB107" s="29">
-        <v>129.95180880969659</v>
-      </c>
-      <c r="DC107" s="9"/>
+        <v>129.99598148395009</v>
+      </c>
+      <c r="DC107" s="29">
+        <v>125.03636702321785</v>
+      </c>
       <c r="DD107" s="9"/>
       <c r="DE107" s="9"/>
       <c r="DF107" s="9"/>
@@ -14749,9 +14823,11 @@
         <v>121.20017822819085</v>
       </c>
       <c r="DB108" s="29">
-        <v>117.7196426002636</v>
-      </c>
-      <c r="DC108" s="9"/>
+        <v>117.75232637531636</v>
+      </c>
+      <c r="DC108" s="29">
+        <v>123.30429576895638</v>
+      </c>
       <c r="DD108" s="9"/>
       <c r="DE108" s="9"/>
       <c r="DF108" s="9"/>
@@ -15115,9 +15191,11 @@
         <v>108.30139280382878</v>
       </c>
       <c r="DB109" s="29">
-        <v>132.37642402911388</v>
-      </c>
-      <c r="DC109" s="9"/>
+        <v>132.41078150980604</v>
+      </c>
+      <c r="DC109" s="29">
+        <v>127.98889723889731</v>
+      </c>
       <c r="DD109" s="9"/>
       <c r="DE109" s="9"/>
       <c r="DF109" s="9"/>
@@ -15634,9 +15712,11 @@
         <v>115.34860073887199</v>
       </c>
       <c r="DB111" s="29">
-        <v>124.8753027357419</v>
-      </c>
-      <c r="DC111" s="9"/>
+        <v>124.9289154444364</v>
+      </c>
+      <c r="DC111" s="29">
+        <v>125.19608272742171</v>
+      </c>
       <c r="DD111" s="9"/>
       <c r="DE111" s="9"/>
       <c r="DF111" s="9"/>
@@ -15790,6 +15870,7 @@
       <c r="CZ112" s="18"/>
       <c r="DA112" s="18"/>
       <c r="DB112" s="18"/>
+      <c r="DC112" s="18"/>
     </row>
     <row r="113" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A113" s="11"/>
@@ -15898,7 +15979,7 @@
       <c r="CZ113" s="3"/>
       <c r="DA113" s="3"/>
       <c r="DB113" s="3"/>
-      <c r="DC113" s="9"/>
+      <c r="DC113" s="3"/>
       <c r="DD113" s="9"/>
       <c r="DE113" s="9"/>
       <c r="DF113" s="9"/>
@@ -16262,9 +16343,11 @@
         <v>114.9509895048661</v>
       </c>
       <c r="DB114" s="29">
-        <v>125.71206497482225</v>
-      </c>
-      <c r="DC114" s="9"/>
+        <v>125.81481065922713</v>
+      </c>
+      <c r="DC114" s="29">
+        <v>140.65909734580291</v>
+      </c>
       <c r="DD114" s="9"/>
       <c r="DE114" s="9"/>
       <c r="DF114" s="9"/>
@@ -16418,6 +16501,7 @@
       <c r="CZ115" s="13"/>
       <c r="DA115" s="13"/>
       <c r="DB115" s="13"/>
+      <c r="DC115" s="13"/>
     </row>
     <row r="116" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A116" s="19" t="s">
@@ -16441,7 +16525,7 @@
     </row>
     <row r="122" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="124" spans="1:152" x14ac:dyDescent="0.2">
@@ -16451,7 +16535,7 @@
     </row>
     <row r="125" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="126" spans="1:152" x14ac:dyDescent="0.2">
@@ -16620,6 +16704,7 @@
       <c r="DB128" s="30">
         <v>2026</v>
       </c>
+      <c r="DC128" s="30"/>
     </row>
     <row r="129" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
@@ -16939,6 +17024,9 @@
       </c>
       <c r="DB129" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC129" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17261,9 +17349,11 @@
         <v>25.205734832062269</v>
       </c>
       <c r="DB131" s="29">
-        <v>18.855507337013471</v>
-      </c>
-      <c r="DC131" s="9"/>
+        <v>18.796633750630466</v>
+      </c>
+      <c r="DC131" s="29">
+        <v>39.143112728541077</v>
+      </c>
       <c r="DD131" s="9"/>
       <c r="DE131" s="9"/>
       <c r="DF131" s="9"/>
@@ -17627,9 +17717,11 @@
         <v>38.385793908998608</v>
       </c>
       <c r="DB132" s="29">
-        <v>45.420260124929676</v>
-      </c>
-      <c r="DC132" s="9"/>
+        <v>45.304343909502698</v>
+      </c>
+      <c r="DC132" s="29">
+        <v>34.387359512092921</v>
+      </c>
       <c r="DD132" s="9"/>
       <c r="DE132" s="9"/>
       <c r="DF132" s="9"/>
@@ -17993,9 +18085,11 @@
         <v>36.408471258939116</v>
       </c>
       <c r="DB133" s="29">
-        <v>35.724232538056846</v>
-      </c>
-      <c r="DC133" s="9"/>
+        <v>35.899022339866839</v>
+      </c>
+      <c r="DC133" s="29">
+        <v>26.469527759366002</v>
+      </c>
       <c r="DD133" s="9"/>
       <c r="DE133" s="9"/>
       <c r="DF133" s="9"/>
@@ -18514,7 +18608,9 @@
       <c r="DB135" s="29">
         <v>100</v>
       </c>
-      <c r="DC135" s="9"/>
+      <c r="DC135" s="29">
+        <v>100</v>
+      </c>
       <c r="DD135" s="9"/>
       <c r="DE135" s="9"/>
       <c r="DF135" s="9"/>
@@ -18668,6 +18764,7 @@
       <c r="CZ136" s="18"/>
       <c r="DA136" s="18"/>
       <c r="DB136" s="18"/>
+      <c r="DC136" s="18"/>
     </row>
     <row r="137" spans="1:152" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="11"/>
@@ -18776,7 +18873,7 @@
       <c r="CZ137" s="3"/>
       <c r="DA137" s="3"/>
       <c r="DB137" s="3"/>
-      <c r="DC137" s="9"/>
+      <c r="DC137" s="3"/>
       <c r="DD137" s="9"/>
       <c r="DE137" s="9"/>
       <c r="DF137" s="9"/>
@@ -18930,7 +19027,7 @@
       <c r="CZ138" s="3"/>
       <c r="DA138" s="3"/>
       <c r="DB138" s="3"/>
-      <c r="DC138" s="9"/>
+      <c r="DC138" s="3"/>
       <c r="DD138" s="9"/>
       <c r="DE138" s="9"/>
       <c r="DF138" s="9"/>
@@ -19084,6 +19181,7 @@
       <c r="CZ139" s="13"/>
       <c r="DA139" s="13"/>
       <c r="DB139" s="13"/>
+      <c r="DC139" s="13"/>
     </row>
     <row r="140" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A140" s="19" t="s">
@@ -19413,7 +19511,7 @@
     </row>
     <row r="146" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="148" spans="1:152" x14ac:dyDescent="0.2">
@@ -19423,7 +19521,7 @@
     </row>
     <row r="149" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="150" spans="1:152" x14ac:dyDescent="0.2">
@@ -19592,6 +19690,7 @@
       <c r="DB152" s="30">
         <v>2026</v>
       </c>
+      <c r="DC152" s="30"/>
     </row>
     <row r="153" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A153" s="6" t="s">
@@ -19911,6 +20010,9 @@
       </c>
       <c r="DB153" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC153" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20233,9 +20335,11 @@
         <v>24.689899947121607</v>
       </c>
       <c r="DB155" s="29">
-        <v>18.118925842684138</v>
-      </c>
-      <c r="DC155" s="9"/>
+        <v>18.06396660624835</v>
+      </c>
+      <c r="DC155" s="29">
+        <v>39.193112340358091</v>
+      </c>
       <c r="DD155" s="9"/>
       <c r="DE155" s="9"/>
       <c r="DF155" s="9"/>
@@ -20599,9 +20703,11 @@
         <v>36.532517364102532</v>
       </c>
       <c r="DB156" s="29">
-        <v>48.181158285508083</v>
-      </c>
-      <c r="DC156" s="9"/>
+        <v>48.065483916607874</v>
+      </c>
+      <c r="DC156" s="29">
+        <v>34.914945009867729</v>
+      </c>
       <c r="DD156" s="9"/>
       <c r="DE156" s="9"/>
       <c r="DF156" s="9"/>
@@ -20965,9 +21071,11 @@
         <v>38.777582688775844</v>
       </c>
       <c r="DB157" s="29">
-        <v>33.699915871807768</v>
-      </c>
-      <c r="DC157" s="9"/>
+        <v>33.870549477143769</v>
+      </c>
+      <c r="DC157" s="29">
+        <v>25.89194264977419</v>
+      </c>
       <c r="DD157" s="9"/>
       <c r="DE157" s="9"/>
       <c r="DF157" s="9"/>
@@ -21486,7 +21594,9 @@
       <c r="DB159" s="29">
         <v>100</v>
       </c>
-      <c r="DC159" s="9"/>
+      <c r="DC159" s="29">
+        <v>100</v>
+      </c>
       <c r="DD159" s="9"/>
       <c r="DE159" s="9"/>
       <c r="DF159" s="9"/>
@@ -21640,6 +21750,7 @@
       <c r="CZ160" s="18"/>
       <c r="DA160" s="18"/>
       <c r="DB160" s="18"/>
+      <c r="DC160" s="18"/>
     </row>
     <row r="161" spans="1:152" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="11"/>
@@ -21748,7 +21859,7 @@
       <c r="CZ161" s="3"/>
       <c r="DA161" s="3"/>
       <c r="DB161" s="3"/>
-      <c r="DC161" s="9"/>
+      <c r="DC161" s="3"/>
       <c r="DD161" s="9"/>
       <c r="DE161" s="9"/>
       <c r="DF161" s="9"/>
@@ -21902,7 +22013,7 @@
       <c r="CZ162" s="3"/>
       <c r="DA162" s="3"/>
       <c r="DB162" s="3"/>
-      <c r="DC162" s="9"/>
+      <c r="DC162" s="3"/>
       <c r="DD162" s="9"/>
       <c r="DE162" s="9"/>
       <c r="DF162" s="9"/>
@@ -22056,6 +22167,7 @@
       <c r="CZ163" s="13"/>
       <c r="DA163" s="13"/>
       <c r="DB163" s="13"/>
+      <c r="DC163" s="13"/>
     </row>
     <row r="164" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A164" s="19" t="s">
@@ -22071,6 +22183,7 @@
       <c r="CZ165" s="5"/>
       <c r="DA165" s="5"/>
       <c r="DB165" s="5"/>
+      <c r="DC165" s="5"/>
     </row>
     <row r="166" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CX166" s="5"/>
@@ -22078,6 +22191,7 @@
       <c r="CZ166" s="5"/>
       <c r="DA166" s="5"/>
       <c r="DB166" s="5"/>
+      <c r="DC166" s="5"/>
     </row>
     <row r="167" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT167" s="7"/>
@@ -22088,6 +22202,7 @@
       <c r="CZ167" s="7"/>
       <c r="DA167" s="7"/>
       <c r="DB167" s="7"/>
+      <c r="DC167" s="7"/>
     </row>
     <row r="168" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT168" s="7"/>
@@ -22098,6 +22213,7 @@
       <c r="CZ168" s="7"/>
       <c r="DA168" s="7"/>
       <c r="DB168" s="7"/>
+      <c r="DC168" s="7"/>
     </row>
     <row r="169" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT169" s="7"/>
@@ -22108,6 +22224,7 @@
       <c r="CZ169" s="7"/>
       <c r="DA169" s="7"/>
       <c r="DB169" s="7"/>
+      <c r="DC169" s="7"/>
     </row>
     <row r="170" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT170" s="7"/>
@@ -22118,6 +22235,7 @@
       <c r="CZ170" s="7"/>
       <c r="DA170" s="7"/>
       <c r="DB170" s="7"/>
+      <c r="DC170" s="7"/>
     </row>
     <row r="171" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT171" s="7"/>
@@ -22128,22 +22246,12 @@
       <c r="CZ171" s="7"/>
       <c r="DA171" s="7"/>
       <c r="DB171" s="7"/>
+      <c r="DC171" s="7"/>
     </row>
     <row r="172" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CT172" s="7"/>
       <c r="CU172" s="7"/>
       <c r="CV172" s="7"/>
-      <c r="CX172" s="7"/>
-      <c r="CY172" s="7"/>
-      <c r="CZ172" s="7"/>
-      <c r="DA172" s="7"/>
-      <c r="DB172" s="7"/>
-    </row>
-    <row r="173" spans="1:152" x14ac:dyDescent="0.2">
-      <c r="DB173" s="7"/>
-    </row>
-    <row r="174" spans="1:152" x14ac:dyDescent="0.2">
-      <c r="DB174" s="7"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -22151,9 +22259,9 @@
   <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="48" max="105" man="1"/>
-    <brk id="96" max="105" man="1"/>
-    <brk id="119" max="105" man="1"/>
+    <brk id="48" max="106" man="1"/>
+    <brk id="96" max="106" man="1"/>
+    <brk id="119" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>